--- a/Ficha de Metadados Eixo 6.xlsx
+++ b/Ficha de Metadados Eixo 6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rais\Rais\Para_readme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32AEC91-1EA7-4BF6-8743-B1B0119F5619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4640A16-53F0-4B60-88AF-40D6BD13F2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="704" xr2:uid="{A1703714-03EB-44BC-9D7E-945BFE928E25}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="704" activeTab="4" xr2:uid="{A1703714-03EB-44BC-9D7E-945BFE928E25}"/>
   </bookViews>
   <sheets>
     <sheet name="Capa" sheetId="24" r:id="rId1"/>
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="511">
   <si>
     <t>2003-2013</t>
   </si>
@@ -483,21 +483,6 @@
     <t>Victor da Silva Oliveira</t>
   </si>
   <si>
-    <t>O projeto produz indicadores de trabalho para a Economia Criativa a partir de bases administrativas (RAIS Vínculos, RAIS Estabelecimentos, Novo CAGED) e da pesquisa de Indicadores Culturais do IBGE (Tabela 6.4 — ocupação no setor cultural, formal e informal), com deflação monetária pelo IPCA.
-Objetivos:
-1) Processar microdados do CAGED e calcular métricas mensais de vínculos, movimentações líquidas e massa salarial (teto de R$ 1.000.000 no fluxo salarial), com deflação para dezembro de 2024.
-2) Extrair e estruturar taxas de formalidade/informalidade (Brasil, UFs e capitais) a partir da Tabela 6.4 do IBGE.
-3) Incorporar estimativas de informalidade ao pipeline do CAGED e da RAIS (vínculos informais = total × (1 − TF)).
-4) Reconstruir estoques de vínculos e massa salarial da RAIS por setor e calcular os índices de acompanhamento (vínculos e salarial), base 100 = dezembro/2024, por frente (Brasil, UF, Capital; Total e Economia Criativa).
-5) Produzir perfis dos vínculos da Economia Criativa de 2025 por sexo, raça/cor, escolaridade, faixa etária, indicador de deficiência, porte, natureza jurídica, domínio cultural e geografia (municípios/capitais).
-6) Processar estabelecimentos da RAIS por natureza jurídica (categoria) e porte, e exportar os CSVs finais dos scripts "6.x".
-Pontos de atenção:
-- Os scripts contêm caminhos absolutos do ambiente original de desenvolvimento (E:\... , D:\...); recomenda-se substituí-los por caminhos configuráveis (DATA_DIR / paths.py) antes da replicação.
-- Arquivos auxiliares obrigatórios: CNAE-ibge.xlsx (lista de CNAE da EC e Domínio Cultural) e municipios.xlsx, além de IPCA_mensal.xls e Informalidade2.xlsx.
-- As taxas de informalidade de 2025 e 2026 usadas no ajuste (TF) devem ser replicadas/confirmadas conforme a atualização da Tabela 6.4 do IBGE.
-- No repositório, versionar apenas os CSVs finais dos scripts "6.x" em outputs/tables/. Dados brutos e bases auxiliares não devem ser versionados.</t>
-  </si>
-  <si>
     <t>RAIS — Vínculos</t>
   </si>
   <si>
@@ -561,30 +546,18 @@
     <t>IBGE/SIIC — Tabela 6.4 (Indicadores Culturais)</t>
   </si>
   <si>
-    <t>Ocupação no setor cultural (formal e informal). Fornece taxas de formalidade/informalidade por Brasil, UF e capitais.</t>
-  </si>
-  <si>
     <t>Estatística / Pesquisa</t>
   </si>
   <si>
-    <t>2012–2024 (série)</t>
-  </si>
-  <si>
     <t>~18 meses</t>
   </si>
   <si>
-    <t>Extração e padronização das colunas Escopo/Escala/Recorte/Ano/Formal/Informal; normalização de percentuais p/ 0–1</t>
-  </si>
-  <si>
     <t>Download manual (XLSX)</t>
   </si>
   <si>
     <t>https://www.ibge.gov.br/estatisticas/multidominio/cultura-recreacao-e-esporte/9388-indicadores-culturais.html</t>
   </si>
   <si>
-    <t>Confirmar atualização da Tabela 6.4 p/ 2024; replicar TF de 2024</t>
-  </si>
-  <si>
     <t>IPCA (IBGE)</t>
   </si>
   <si>
@@ -651,12 +624,6 @@
     <t>IND_001 — Estoque de vínculos da EC (formal)</t>
   </si>
   <si>
-    <t>IND_002 — Vínculos formais e informais estimados da EC</t>
-  </si>
-  <si>
-    <t>total_vinculos + total_vinculos_informais_estimado, por ano</t>
-  </si>
-  <si>
     <t>IND_003 — Estoque de vínculos por setor</t>
   </si>
   <si>
@@ -741,15 +708,9 @@
     <t>IND_017 — Participação da EC nos vínculos por Capital</t>
   </si>
   <si>
-    <t>total_cultura / total_geral × 100, por capital, 2024</t>
-  </si>
-  <si>
     <t>IND_018 — Participação da EC nos vínculos por UF</t>
   </si>
   <si>
-    <t>total_cultura / total_geral × 100, por UF, 2024</t>
-  </si>
-  <si>
     <t>IND_019 — EC por 1.000 trabalhadores (municípios)</t>
   </si>
   <si>
@@ -825,9 +786,6 @@
     <t>Série histórica RAIS 2016–2025. Realiza o somatório de vínculos formais do setor cultural a partir das métricas por grupo (saída 6_5.csv/6.7.csv).</t>
   </si>
   <si>
-    <t>Soma o estoque formal à estimativa de informais (= total × (1−TF)) para a EC, reproduzindo a base do gráfico de vínculos (6_5.csv/6_6.csv).</t>
-  </si>
-  <si>
     <t>Agrega vínculos para Economia Criativa, Agricultura, Indústria extrativa e Construção Civil (2016–2025), com renomeação de exibição (6.7.csv).</t>
   </si>
   <si>
@@ -873,12 +831,6 @@
     <t>Conversão de % para 0–1; usada no cálculo do fator_TF nos índices (derivado em 03/04_*IRCA_frentes.py).</t>
   </si>
   <si>
-    <t>Identifica pares Total/EC em grupo (prefixo "Capital") e soma formal+informal (6.10.1.csv).</t>
-  </si>
-  <si>
-    <t>Mesma lógica, prefixo "UF" (6.10.2.csv).</t>
-  </si>
-  <si>
     <t>Conta vínculos da EC (CNAE da EC) e total por município via municipios.xlsx (ec_por_1000_trabalhadores_municipios.csv).</t>
   </si>
   <si>
@@ -1407,15 +1359,9 @@
     <t>proporção (0–1)</t>
   </si>
   <si>
-    <t>to_numeric; se max&gt;1,5 → divide por 100</t>
-  </si>
-  <si>
     <t>IND_013, IND_016</t>
   </si>
   <si>
-    <t>Base da TF</t>
-  </si>
-  <si>
     <t>Informal - Total</t>
   </si>
   <si>
@@ -1425,9 +1371,6 @@
     <t>VAR032</t>
   </si>
   <si>
-    <t>to_numeric; normalização 0–1</t>
-  </si>
-  <si>
     <t>grupo</t>
   </si>
   <si>
@@ -1557,15 +1500,9 @@
     <t>total_vinculos_informais_estimado</t>
   </si>
   <si>
-    <t>Vínculos informais estimados</t>
-  </si>
-  <si>
     <t>VAR041</t>
   </si>
   <si>
-    <t>total_vinculos × (1 − TF)</t>
-  </si>
-  <si>
     <t>RAIS/CAGED+IBGE</t>
   </si>
   <si>
@@ -1692,22 +1629,7 @@
     <t>Saída padrão decimal (0,025 = 2,5%)</t>
   </si>
   <si>
-    <t>participacao_ec / ec_por_1000_trabalhadores</t>
-  </si>
-  <si>
-    <t>Participação da EC (%) e EC por 1.000</t>
-  </si>
-  <si>
     <t>VAR048</t>
-  </si>
-  <si>
-    <t>% / por mil</t>
-  </si>
-  <si>
-    <t>2024–2025</t>
-  </si>
-  <si>
-    <t>total_cultura / total_geral × 100; ec / total × 1.000</t>
   </si>
   <si>
     <t>IND_017–019</t>
@@ -1774,6 +1696,181 @@
   <si>
     <t>Cultura em números Eixo 6 -  ECONOMIA CRIATIVA, ECONOMIA SOLIDÁRIA, TRABALHO, EMPREGO, RENDA E PROTEÇÃO SOCIAL</t>
   </si>
+  <si>
+    <t>O projeto produz indicadores de trabalho para a Economia Criativa a partir de bases administrativas (RAIS Vínculos, RAIS Estabelecimentos e Novo CAGED) e da Tabela 6.4 da pesquisa de Indicadores Culturais do IBGE, que apresenta informações sobre ocupação cultural formal e informal. Para o período processado de 2015 a 2024, a tabela também fornece totais de trabalhadores do conjunto da economia e do setor cultural. Os valores monetários são deflacionados pelo IPCA.
+Objetivos:
+1) Processar microdados do CAGED e calcular métricas mensais de vínculos, movimentações líquidas e massa salarial (teto de R$ 1.000.000 no fluxo salarial), com deflação para dezembro de 2024.
+2) Extrair e estruturar, para 2015–2024, as taxas de formalidade e informalidade e os totais de trabalhadores da Tabela 6.4 do IBGE, por escopo (Total e Cultura) e recorte nacional, estadual e municipal — neste último caso, para as capitais.
+3) Incorporar às métricas da RAIS os totais de trabalhadores da Tabela 6.4 do IBGE, associando os registros por ano, escopo, escala e recorte. Na base processada, total_vinculos_informais_estimado recebe o total de trabalhadores da Cultura informado pelo IBGE, e total_vinculos_ibge recebe o total de trabalhadores do IBGE.
+4) Reconstruir estoques de vínculos e massa salarial da RAIS por setor e calcular os índices de acompanhamento (vínculos e salarial), base 100 = dezembro/2024, por frente (Brasil, UF, Capital; Total e Economia Criativa).
+5) Produzir perfis dos vínculos da Economia Criativa de 2025 por sexo, raça/cor, escolaridade, faixa etária, indicador de deficiência, porte, natureza jurídica, domínio cultural e geografia (municípios/capitais).
+6) Processar estabelecimentos da RAIS por natureza jurídica (categoria) e porte, e exportar os CSVs finais dos scripts "6.x".
+Pontos de atenção:
+- Os scripts contêm caminhos absolutos do ambiente original de desenvolvimento (E:\... , D:\...); recomenda-se substituí-los por caminhos configuráveis (DATA_DIR / paths.py) antes da replicação.
+- Arquivos auxiliares obrigatórios: CNAE-ibge.xlsx (lista de CNAE da EC e Domínio Cultural) e municipios.xlsx, além de IPCA_mensal.xls e Informalidade2.xlsx.
+- A extração da Tabela 6.4 implementada no script contempla 2015–2024. Os totais associados às métricas ficam em branco para 2025 e para grupos sem correspondência na tabela; os valores não são replicados automaticamente de 2024.
+- As linhas de 2015 acrescentadas ao arquivo de métricas recebem os totais disponíveis na Tabela 6.4; as variáveis provenientes exclusivamente da RAIS permanecem vazias quando não há registro correspondente.
+- No repositório, versionar apenas os CSVs finais dos scripts "6.x" em outputs/tables/. Dados brutos e bases auxiliares não devem ser versionados.</t>
+  </si>
+  <si>
+    <t>Tabela sobre ocupação no setor cultural, com informações de formalidade, informalidade e totais de trabalhadores para o conjunto da economia e para o setor cultural, por Brasil, UFs e municípios de capitais.</t>
+  </si>
+  <si>
+    <t>2015–2024 (série)</t>
+  </si>
+  <si>
+    <t>Extração das abas anuais da Tabela 6.4, com padronização de Escopo, Escala, Recorte e Ano. As taxas de formalidade e informalidade são convertidas de percentual para proporção (0–1). Os totais de trabalhadores, informados em milhares, são multiplicados por 1.000. São gerados registros para os escopos Total e Cultura; as grandes regiões são ignoradas, e as localidades são classificadas como Brasil, UF ou município de capital.</t>
+  </si>
+  <si>
+    <t>Confirmar se o arquivo de entrada contém a versão mais recente da Tabela 6.4 e validar o período efetivamente processado. Conferir a correspondência de Brasil, UFs e capitais e a conversão dos totais de trabalhadores de milhares para unidades.</t>
+  </si>
+  <si>
+    <t>IND_002 — Total de trabalhadores da Cultura informado pelo IBGE</t>
+  </si>
+  <si>
+    <t>Utiliza o valor de Trabalhadores - Cultura da Tabela 6.4 do IBGE, associado às métricas por ano e grupo. O campo é mantido na base com o nome total_vinculos_informais_estimado por compatibilidade.</t>
+  </si>
+  <si>
+    <t>O script 02 associa o total de trabalhadores do setor cultural informado pelo IBGE ao grupo correspondente. O 6_5.py exporta esse valor e calcula sua variação anual, sem somá-lo aos vínculos formais da RAIS nem estimá-lo a partir da taxa de informalidade. Os valores sem correspondência ficam em branco.</t>
+  </si>
+  <si>
+    <t>Trabalhadores - Cultura / Trabalhadores - Total, por capital, para 2024. O resultado é armazenado como proporção; para apresentá-lo em percentual, multiplicar por 100.</t>
+  </si>
+  <si>
+    <t>Associa os totais de trabalhadores da Cultura e do conjunto da economia informados na Tabela 6.4 do IBGE. A saída identifica as capitais por código municipal do IBGE. Valores ausentes não são convertidos em zero.</t>
+  </si>
+  <si>
+    <t>Trabalhadores - Cultura / Trabalhadores - Total, por UF, para 2024. O resultado é armazenado como proporção; para apresentá-lo em percentual, multiplicar por 100.</t>
+  </si>
+  <si>
+    <t>Associa os totais de trabalhadores da Cultura e do conjunto da economia informados na Tabela 6.4 do IBGE. A saída identifica as UFs por sigla. Valores ausentes não são convertidos em zero.</t>
+  </si>
+  <si>
+    <t>IND_031 — Participação dos trabalhadores da Cultura no total nacional</t>
+  </si>
+  <si>
+    <t>Trabalhadores - Cultura / Trabalhadores - Total, por ano.</t>
+  </si>
+  <si>
+    <t>Usa os totais de trabalhadores da Cultura e do conjunto da economia informados pelo IBGE. A razão é armazenada como proporção; para apresentação em percentual, multiplicar por 100. Valores sem correspondência ficam em branco.</t>
+  </si>
+  <si>
+    <t>2015–2024</t>
+  </si>
+  <si>
+    <t>Extraído da Tabela 6.4 para os escopos Total e Cultura; percentual convertido em proporção pela divisão por 100.</t>
+  </si>
+  <si>
+    <t>o script processa anos a partir de 2015, mas não fixa 2024 como limite superior. Confirme o último ano das abas do arquivo utilizado antes de registrar 2015–2024.</t>
+  </si>
+  <si>
+    <t>VAR049</t>
+  </si>
+  <si>
+    <t>total_vinculos_rais</t>
+  </si>
+  <si>
+    <t>Estoque de vínculos formais da RAIS, preservado com esse nome na base processada que incorpora os totais do IBGE.</t>
+  </si>
+  <si>
+    <t>Recebe os valores originais de total_vinculos da base de métricas; o script 02 renomeia a coluna para total_vinculos_rais.</t>
+  </si>
+  <si>
+    <t>Nas linhas de 2015 acrescentadas pelo script 02, esta variável fica vazia quando não há valor correspondente da RAIS.</t>
+  </si>
+  <si>
+    <t>Total de trabalhadores da Cultura informado pela Tabela 6.4 do IBGE e armazenado com o nome legado total_vinculos_informais_estimado.</t>
+  </si>
+  <si>
+    <t>trabalhadores</t>
+  </si>
+  <si>
+    <t>2015–2025; valores associados do IBGE até 2024, sem preenchimento para 2025.</t>
+  </si>
+  <si>
+    <t>Recebe diretamente Trabalhadores - Cultura da Tabela 6.4, associado por ano, escopo, escala e recorte. Não é calculado por meio de total_vinculos × (1 − TF).</t>
+  </si>
+  <si>
+    <t>IBGE/SIIC — Tabela 6.4, associado à base de métricas da RAIS.</t>
+  </si>
+  <si>
+    <t>O nome foi mantido por compatibilidade, mas o conteúdo é o total de trabalhadores da Cultura informado pelo IBGE, não uma contagem exclusiva de trabalhadores informais.</t>
+  </si>
+  <si>
+    <t>participacao_ec</t>
+  </si>
+  <si>
+    <t>Razão entre o total de trabalhadores da Cultura e o total de trabalhadores do IBGE.</t>
+  </si>
+  <si>
+    <t>Trabalhadores - Cultura / Trabalhadores - Total. O resultado é uma razão; multiplicar por 100 apenas para apresentá-lo como percentual.</t>
+  </si>
+  <si>
+    <t>2015–2025 para a série nacional; valores do IBGE associados até 2024. Capitais e UFs: 2024.</t>
+  </si>
+  <si>
+    <t>Derivado da Tabela 6.4 do IBGE.</t>
+  </si>
+  <si>
+    <t>A série nacional é gerada pelo 6_6.py; capitais e UFs são geradas pelo 6_10.py. Valores ausentes não são substituídos por zero.</t>
+  </si>
+  <si>
+    <t>Trabalhadores - Total</t>
+  </si>
+  <si>
+    <t>Total de trabalhadores do conjunto da economia informado na Tabela 6.4.</t>
+  </si>
+  <si>
+    <t>VAR050</t>
+  </si>
+  <si>
+    <t>VAR051</t>
+  </si>
+  <si>
+    <t>VAR052</t>
+  </si>
+  <si>
+    <t>VAR053</t>
+  </si>
+  <si>
+    <t>Valor da tabela, informado em milhares e multiplicado por 1.000.</t>
+  </si>
+  <si>
+    <t>IBGE/SIIC — Tabela 6.4</t>
+  </si>
+  <si>
+    <t>Trabalhadores - Cultura</t>
+  </si>
+  <si>
+    <t>Total de trabalhadores do setor cultural informado na Tabela 6.4.</t>
+  </si>
+  <si>
+    <t>total_vinculos_ibge</t>
+  </si>
+  <si>
+    <t>Total de trabalhadores do conjunto da economia associado à base de métricas.</t>
+  </si>
+  <si>
+    <t>2015–2025; valores associados do IBGE até 2024</t>
+  </si>
+  <si>
+    <t>Recebe Trabalhadores - Total, associado por ano, escopo, escala e recorte.</t>
+  </si>
+  <si>
+    <t>pct_variacao_anual</t>
+  </si>
+  <si>
+    <t>Variação anual do total de trabalhadores da Cultura associado à base.</t>
+  </si>
+  <si>
+    <t>2015–2025; sem valor quando não há observação válida</t>
+  </si>
+  <si>
+    <t>Calculada como variação percentual anual de total_vinculos_informais_estimado, cujo conteúdo é Trabalhadores - Cultura do IBGE.</t>
+  </si>
+  <si>
+    <t>Derivado da Tabela 6.4</t>
+  </si>
 </sst>
 </file>
 
@@ -1782,7 +1879,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -1968,6 +2065,11 @@
     <font>
       <b/>
       <i/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -2528,7 +2630,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2635,9 +2737,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2742,69 +2841,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="10" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2823,50 +2859,16 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="10" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2877,12 +2879,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2891,12 +2887,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2907,6 +2897,114 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -3337,11 +3435,11 @@
     </row>
     <row r="2" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -3367,8 +3465,8 @@
         <v>52</v>
       </c>
       <c r="C4" s="6"/>
-      <c r="D4" s="132" t="s">
-        <v>478</v>
+      <c r="D4" s="94" t="s">
+        <v>456</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -3463,11 +3561,11 @@
     </row>
     <row r="11" spans="1:10" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="96" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -3489,11 +3587,11 @@
     </row>
     <row r="13" spans="1:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
-      <c r="B13" s="80" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="81"/>
-      <c r="D13" s="82"/>
+      <c r="B13" s="97" t="s">
+        <v>457</v>
+      </c>
+      <c r="C13" s="98"/>
+      <c r="D13" s="99"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
@@ -3503,9 +3601,9 @@
     </row>
     <row r="14" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
-      <c r="B14" s="83"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="85"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="101"/>
+      <c r="D14" s="102"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
@@ -3515,9 +3613,9 @@
     </row>
     <row r="15" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="84"/>
-      <c r="D15" s="85"/>
+      <c r="B15" s="100"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="102"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
@@ -3527,9 +3625,9 @@
     </row>
     <row r="16" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
-      <c r="B16" s="83"/>
-      <c r="C16" s="84"/>
-      <c r="D16" s="85"/>
+      <c r="B16" s="100"/>
+      <c r="C16" s="101"/>
+      <c r="D16" s="102"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
@@ -3539,9 +3637,9 @@
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
-      <c r="B17" s="83"/>
-      <c r="C17" s="84"/>
-      <c r="D17" s="85"/>
+      <c r="B17" s="100"/>
+      <c r="C17" s="101"/>
+      <c r="D17" s="102"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
@@ -3551,9 +3649,9 @@
     </row>
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
-      <c r="B18" s="83"/>
-      <c r="C18" s="84"/>
-      <c r="D18" s="85"/>
+      <c r="B18" s="100"/>
+      <c r="C18" s="101"/>
+      <c r="D18" s="102"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -3563,9 +3661,9 @@
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
-      <c r="B19" s="83"/>
-      <c r="C19" s="84"/>
-      <c r="D19" s="85"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="102"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
@@ -3575,9 +3673,9 @@
     </row>
     <row r="20" spans="1:10" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="85"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="101"/>
+      <c r="D20" s="102"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
@@ -3587,9 +3685,9 @@
     </row>
     <row r="21" spans="1:10" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
-      <c r="B21" s="83"/>
-      <c r="C21" s="84"/>
-      <c r="D21" s="85"/>
+      <c r="B21" s="100"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="102"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
@@ -3599,9 +3697,9 @@
     </row>
     <row r="22" spans="1:10" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
-      <c r="B22" s="83"/>
-      <c r="C22" s="84"/>
-      <c r="D22" s="85"/>
+      <c r="B22" s="100"/>
+      <c r="C22" s="101"/>
+      <c r="D22" s="102"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -3611,9 +3709,9 @@
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
-      <c r="B23" s="83"/>
-      <c r="C23" s="84"/>
-      <c r="D23" s="85"/>
+      <c r="B23" s="100"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="102"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -3623,9 +3721,9 @@
     </row>
     <row r="24" spans="1:10" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6"/>
-      <c r="B24" s="83"/>
-      <c r="C24" s="84"/>
-      <c r="D24" s="85"/>
+      <c r="B24" s="100"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="102"/>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -3635,9 +3733,9 @@
     </row>
     <row r="25" spans="1:10" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
-      <c r="B25" s="83"/>
-      <c r="C25" s="84"/>
-      <c r="D25" s="85"/>
+      <c r="B25" s="100"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="102"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
@@ -3647,9 +3745,9 @@
     </row>
     <row r="26" spans="1:10" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
-      <c r="B26" s="83"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="85"/>
+      <c r="B26" s="100"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="102"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
@@ -3659,9 +3757,9 @@
     </row>
     <row r="27" spans="1:10" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
-      <c r="B27" s="83"/>
-      <c r="C27" s="84"/>
-      <c r="D27" s="85"/>
+      <c r="B27" s="100"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="102"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
@@ -3671,9 +3769,9 @@
     </row>
     <row r="28" spans="1:10" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
-      <c r="B28" s="83"/>
-      <c r="C28" s="84"/>
-      <c r="D28" s="85"/>
+      <c r="B28" s="100"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="102"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
@@ -3683,9 +3781,9 @@
     </row>
     <row r="29" spans="1:10" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
-      <c r="B29" s="83"/>
-      <c r="C29" s="84"/>
-      <c r="D29" s="85"/>
+      <c r="B29" s="100"/>
+      <c r="C29" s="101"/>
+      <c r="D29" s="102"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
@@ -3695,9 +3793,9 @@
     </row>
     <row r="30" spans="1:10" ht="409.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="B30" s="86"/>
-      <c r="C30" s="87"/>
-      <c r="D30" s="88"/>
+      <c r="B30" s="103"/>
+      <c r="C30" s="104"/>
+      <c r="D30" s="105"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
@@ -3842,10 +3940,10 @@
     </row>
     <row r="2" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="95" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="78"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -3866,10 +3964,10 @@
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="61" t="s">
         <v>32</v>
       </c>
       <c r="D4" s="6"/>
@@ -3881,10 +3979,10 @@
     </row>
     <row r="5" spans="1:9" ht="112.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="63" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="6"/>
@@ -3896,10 +3994,10 @@
     </row>
     <row r="6" spans="1:9" ht="112.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="66" t="s">
+      <c r="C6" s="65" t="s">
         <v>60</v>
       </c>
       <c r="D6" s="6"/>
@@ -3911,10 +4009,10 @@
     </row>
     <row r="7" spans="1:9" ht="112.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="66" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="6"/>
@@ -4046,86 +4144,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="70"/>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
+      <c r="A1" s="69"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
     </row>
     <row r="2" spans="1:13" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="70"/>
-      <c r="B2" s="76" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="70"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="69"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="72"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="72"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="72"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="71"/>
     </row>
     <row r="5" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="72"/>
-      <c r="B5" s="77" t="s">
+      <c r="A5" s="71"/>
+      <c r="B5" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="72"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="71"/>
     </row>
     <row r="6" spans="1:13" ht="57" x14ac:dyDescent="0.2">
-      <c r="A6" s="72"/>
+      <c r="A6" s="71"/>
       <c r="B6" s="20" t="s">
         <v>10</v>
       </c>
@@ -4159,10 +4257,10 @@
       <c r="L6" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="72"/>
+      <c r="M6" s="71"/>
     </row>
     <row r="7" spans="1:13" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="71"/>
       <c r="B7" s="22" t="s">
         <v>21</v>
       </c>
@@ -4196,252 +4294,252 @@
       <c r="L7" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="72"/>
+      <c r="M7" s="71"/>
     </row>
     <row r="8" spans="1:13" ht="45.75" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="72"/>
+      <c r="A8" s="71"/>
       <c r="B8" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="D8" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="98" t="s">
+      <c r="E8" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="97" t="s">
+      <c r="F8" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="97" t="s">
+      <c r="G8" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="G8" s="97" t="s">
+      <c r="H8" s="75" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="97" t="s">
+      <c r="J8" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="K8" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="19"/>
+      <c r="M8" s="71"/>
+    </row>
+    <row r="9" spans="1:13" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="71"/>
+      <c r="B9" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="77" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="78">
+        <v>2025</v>
+      </c>
+      <c r="G9" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8" s="18" t="s">
+      <c r="I9" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="K8" s="96" t="s">
-        <v>75</v>
-      </c>
-      <c r="L8" s="19"/>
-      <c r="M8" s="72"/>
-    </row>
-    <row r="9" spans="1:13" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="72"/>
-      <c r="B9" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="99" t="s">
+      <c r="L9" s="14"/>
+      <c r="M9" s="71"/>
+    </row>
+    <row r="10" spans="1:13" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="71"/>
+      <c r="B10" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="77" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="100" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="100">
-        <v>2025</v>
-      </c>
-      <c r="G9" s="100" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="100" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="13" t="s">
+      <c r="F10" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="J10" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="K9" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="L9" s="14"/>
-      <c r="M9" s="72"/>
-    </row>
-    <row r="10" spans="1:13" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="72"/>
-      <c r="B10" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="99" t="s">
+      <c r="K10" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="L10" s="14"/>
+      <c r="M10" s="71"/>
+    </row>
+    <row r="11" spans="1:13" ht="78.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="71"/>
+      <c r="B11" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="100" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="100" t="s">
-        <v>83</v>
-      </c>
-      <c r="G10" s="100" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" s="100" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="L10" s="14"/>
-      <c r="M10" s="72"/>
-    </row>
-    <row r="11" spans="1:13" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="72"/>
-      <c r="B11" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="F11" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>88</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>91</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>11</v>
       </c>
       <c r="I11" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="M11" s="71"/>
+    </row>
+    <row r="12" spans="1:13" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="71"/>
+      <c r="B12" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="D12" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="E12" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="G12" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="M11" s="72"/>
-    </row>
-    <row r="12" spans="1:13" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="72"/>
-      <c r="B12" s="12" t="s">
+      <c r="J12" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="K12" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="L12" s="14"/>
+      <c r="M12" s="71"/>
+    </row>
+    <row r="13" spans="1:13" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="71"/>
+      <c r="B13" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="13" t="s">
+      <c r="C13" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="G12" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" s="13" t="s">
+      <c r="D13" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="E13" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="G13" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="L12" s="14"/>
-      <c r="M12" s="72"/>
-    </row>
-    <row r="13" spans="1:13" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="72"/>
-      <c r="B13" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="13" t="s">
+      <c r="J13" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="K13" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="13" t="s">
+      <c r="L13" s="14"/>
+      <c r="M13" s="71"/>
+    </row>
+    <row r="14" spans="1:13" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="71"/>
+      <c r="B14" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="C14" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="H13" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="L13" s="14"/>
-      <c r="M13" s="72"/>
-    </row>
-    <row r="14" spans="1:13" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A14" s="72"/>
-      <c r="B14" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>113</v>
-      </c>
       <c r="E14" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G14" s="13"/>
       <c r="I14" s="13" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="L14" s="14"/>
-      <c r="M14" s="72"/>
+      <c r="M14" s="71"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="72"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="12"/>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
@@ -4453,10 +4551,10 @@
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
       <c r="L15" s="14"/>
-      <c r="M15" s="72"/>
+      <c r="M15" s="71"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="72"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="12"/>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
@@ -4468,10 +4566,10 @@
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
       <c r="L16" s="14"/>
-      <c r="M16" s="72"/>
+      <c r="M16" s="71"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="72"/>
+      <c r="A17" s="71"/>
       <c r="B17" s="12"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
@@ -4483,10 +4581,10 @@
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
       <c r="L17" s="14"/>
-      <c r="M17" s="72"/>
+      <c r="M17" s="71"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="72"/>
+      <c r="A18" s="71"/>
       <c r="B18" s="12"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -4498,10 +4596,10 @@
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
       <c r="L18" s="14"/>
-      <c r="M18" s="72"/>
+      <c r="M18" s="71"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="72"/>
+      <c r="A19" s="71"/>
       <c r="B19" s="12"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -4513,10 +4611,10 @@
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
       <c r="L19" s="14"/>
-      <c r="M19" s="72"/>
+      <c r="M19" s="71"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="72"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="12"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -4528,10 +4626,10 @@
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
       <c r="L20" s="14"/>
-      <c r="M20" s="72"/>
+      <c r="M20" s="71"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="72"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="12"/>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -4543,10 +4641,10 @@
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="14"/>
-      <c r="M21" s="72"/>
+      <c r="M21" s="71"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="72"/>
+      <c r="A22" s="71"/>
       <c r="B22" s="12"/>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -4558,10 +4656,10 @@
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
       <c r="L22" s="14"/>
-      <c r="M22" s="72"/>
+      <c r="M22" s="71"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="72"/>
+      <c r="A23" s="71"/>
       <c r="B23" s="12"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -4573,10 +4671,10 @@
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
       <c r="L23" s="14"/>
-      <c r="M23" s="72"/>
+      <c r="M23" s="71"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="72"/>
+      <c r="A24" s="71"/>
       <c r="B24" s="12"/>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -4588,10 +4686,10 @@
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
       <c r="L24" s="14"/>
-      <c r="M24" s="72"/>
+      <c r="M24" s="71"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="72"/>
+      <c r="A25" s="71"/>
       <c r="B25" s="12"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -4603,10 +4701,10 @@
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
       <c r="L25" s="14"/>
-      <c r="M25" s="72"/>
+      <c r="M25" s="71"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="72"/>
+      <c r="A26" s="71"/>
       <c r="B26" s="12"/>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -4618,10 +4716,10 @@
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
       <c r="L26" s="14"/>
-      <c r="M26" s="72"/>
+      <c r="M26" s="71"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="72"/>
+      <c r="A27" s="71"/>
       <c r="B27" s="12"/>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -4633,10 +4731,10 @@
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
       <c r="L27" s="14"/>
-      <c r="M27" s="72"/>
+      <c r="M27" s="71"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="72"/>
+      <c r="A28" s="71"/>
       <c r="B28" s="12"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -4648,10 +4746,10 @@
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
       <c r="L28" s="14"/>
-      <c r="M28" s="72"/>
+      <c r="M28" s="71"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="72"/>
+      <c r="A29" s="71"/>
       <c r="B29" s="12"/>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
@@ -4663,10 +4761,10 @@
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
       <c r="L29" s="14"/>
-      <c r="M29" s="72"/>
+      <c r="M29" s="71"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="72"/>
+      <c r="A30" s="71"/>
       <c r="B30" s="12"/>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -4678,10 +4776,10 @@
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
       <c r="L30" s="14"/>
-      <c r="M30" s="72"/>
+      <c r="M30" s="71"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="72"/>
+      <c r="A31" s="71"/>
       <c r="B31" s="12"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
@@ -4693,10 +4791,10 @@
       <c r="J31" s="13"/>
       <c r="K31" s="13"/>
       <c r="L31" s="14"/>
-      <c r="M31" s="72"/>
+      <c r="M31" s="71"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="72"/>
+      <c r="A32" s="71"/>
       <c r="B32" s="12"/>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
@@ -4708,10 +4806,10 @@
       <c r="J32" s="13"/>
       <c r="K32" s="13"/>
       <c r="L32" s="14"/>
-      <c r="M32" s="72"/>
+      <c r="M32" s="71"/>
     </row>
     <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="72"/>
+      <c r="A33" s="71"/>
       <c r="B33" s="12"/>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -4723,10 +4821,10 @@
       <c r="J33" s="13"/>
       <c r="K33" s="13"/>
       <c r="L33" s="14"/>
-      <c r="M33" s="72"/>
+      <c r="M33" s="71"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="72"/>
+      <c r="A34" s="71"/>
       <c r="B34" s="12"/>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
@@ -4738,10 +4836,10 @@
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
       <c r="L34" s="14"/>
-      <c r="M34" s="72"/>
+      <c r="M34" s="71"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="72"/>
+      <c r="A35" s="71"/>
       <c r="B35" s="12"/>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
@@ -4753,10 +4851,10 @@
       <c r="J35" s="13"/>
       <c r="K35" s="13"/>
       <c r="L35" s="14"/>
-      <c r="M35" s="72"/>
+      <c r="M35" s="71"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="72"/>
+      <c r="A36" s="71"/>
       <c r="B36" s="12"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -4768,10 +4866,10 @@
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
       <c r="L36" s="14"/>
-      <c r="M36" s="72"/>
+      <c r="M36" s="71"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="72"/>
+      <c r="A37" s="71"/>
       <c r="B37" s="12"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -4783,10 +4881,10 @@
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
       <c r="L37" s="14"/>
-      <c r="M37" s="72"/>
+      <c r="M37" s="71"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38" s="72"/>
+      <c r="A38" s="71"/>
       <c r="B38" s="12"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -4798,10 +4896,10 @@
       <c r="J38" s="13"/>
       <c r="K38" s="13"/>
       <c r="L38" s="14"/>
-      <c r="M38" s="72"/>
+      <c r="M38" s="71"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39" s="72"/>
+      <c r="A39" s="71"/>
       <c r="B39" s="12"/>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
@@ -4813,10 +4911,10 @@
       <c r="J39" s="13"/>
       <c r="K39" s="13"/>
       <c r="L39" s="14"/>
-      <c r="M39" s="72"/>
+      <c r="M39" s="71"/>
     </row>
     <row r="40" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="72"/>
+      <c r="A40" s="71"/>
       <c r="B40" s="26"/>
       <c r="C40" s="27"/>
       <c r="D40" s="27"/>
@@ -4828,7 +4926,7 @@
       <c r="J40" s="27"/>
       <c r="K40" s="27"/>
       <c r="L40" s="28"/>
-      <c r="M40" s="72"/>
+      <c r="M40" s="71"/>
     </row>
     <row r="41" spans="1:13" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6"/>
@@ -5341,761 +5439,767 @@
   <dimension ref="A1:N97"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="12.75" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="130" customWidth="1"/>
-    <col min="2" max="2" width="20" style="130" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" style="131" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="130" customWidth="1"/>
-    <col min="5" max="5" width="41.140625" style="130" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="130" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="130" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="130" customWidth="1"/>
-    <col min="9" max="9" width="49.85546875" style="130" customWidth="1"/>
-    <col min="10" max="11" width="49.85546875" style="130" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="2.42578125" style="130" customWidth="1"/>
-    <col min="13" max="14" width="0" style="130" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="130" hidden="1"/>
+    <col min="1" max="1" width="2.42578125" style="92" customWidth="1"/>
+    <col min="2" max="2" width="20" style="92" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" style="93" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="92" customWidth="1"/>
+    <col min="5" max="5" width="41.140625" style="92" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="92" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="92" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="92" customWidth="1"/>
+    <col min="9" max="9" width="49.85546875" style="92" customWidth="1"/>
+    <col min="10" max="11" width="49.85546875" style="92" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="2.42578125" style="92" customWidth="1"/>
+    <col min="13" max="14" width="0" style="92" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="92" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="111"/>
-      <c r="B1" s="111"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="113"/>
-    </row>
-    <row r="2" spans="1:12" s="114" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="113"/>
-      <c r="B2" s="115" t="s">
+    <row r="1" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="80"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="71"/>
+    </row>
+    <row r="2" spans="1:12" s="82" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="71"/>
+      <c r="B2" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="113"/>
-    </row>
-    <row r="3" spans="1:12" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="113"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="113"/>
-    </row>
-    <row r="4" spans="1:12" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="113"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="71"/>
+    </row>
+    <row r="3" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="71"/>
+    </row>
+    <row r="4" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="71"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
-      <c r="L4" s="113"/>
-    </row>
-    <row r="5" spans="1:12" s="114" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="118" t="s">
+      <c r="L4" s="71"/>
+    </row>
+    <row r="5" spans="1:12" s="82" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="112" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="119"/>
-    </row>
-    <row r="6" spans="1:12" s="114" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="120" t="s">
+      <c r="C5" s="112"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="112"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+    </row>
+    <row r="6" spans="1:12" s="82" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="121" t="s">
-        <v>472</v>
-      </c>
-      <c r="D6" s="122" t="s">
+      <c r="C6" s="87" t="s">
+        <v>450</v>
+      </c>
+      <c r="D6" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="123"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="124"/>
-    </row>
-    <row r="7" spans="1:12" s="114" customFormat="1" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="125" t="s">
-        <v>473</v>
-      </c>
-      <c r="C7" s="126" t="s">
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="114"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="88"/>
+    </row>
+    <row r="7" spans="1:12" s="82" customFormat="1" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="89" t="s">
+        <v>451</v>
+      </c>
+      <c r="C7" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="127" t="s">
+      <c r="D7" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="128"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="116"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:12" s="114" customFormat="1" ht="23.25" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" s="82" customFormat="1" ht="23.25" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B8" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="74" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="102" t="s">
-        <v>175</v>
-      </c>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="103"/>
-      <c r="I8" s="104"/>
+        <v>112</v>
+      </c>
+      <c r="C8" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="117" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="119"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:12" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" s="82" customFormat="1" ht="56.25" x14ac:dyDescent="0.2">
       <c r="B9" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" s="93" t="s">
-        <v>176</v>
-      </c>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="94"/>
+        <v>462</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>463</v>
+      </c>
+      <c r="D9" s="120" t="s">
+        <v>464</v>
+      </c>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="120"/>
+      <c r="I9" s="121"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="1:12" s="114" customFormat="1" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" s="82" customFormat="1" ht="22.5" x14ac:dyDescent="0.2">
       <c r="B10" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" s="105" t="s">
-        <v>177</v>
-      </c>
-      <c r="E10" s="106"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="107"/>
+        <v>113</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="122" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="123"/>
+      <c r="H10" s="123"/>
+      <c r="I10" s="124"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="1:12" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B11" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="D11" s="93" t="s">
-        <v>178</v>
-      </c>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="94"/>
+        <v>115</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="120" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="120"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="120"/>
+      <c r="H11" s="120"/>
+      <c r="I11" s="121"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:12" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B12" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="D12" s="93" t="s">
-        <v>179</v>
-      </c>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="94"/>
+        <v>117</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="120" t="s">
+        <v>169</v>
+      </c>
+      <c r="E12" s="120"/>
+      <c r="F12" s="120"/>
+      <c r="G12" s="120"/>
+      <c r="H12" s="120"/>
+      <c r="I12" s="121"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="1:12" s="114" customFormat="1" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" s="82" customFormat="1" ht="22.5" x14ac:dyDescent="0.2">
       <c r="B13" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>181</v>
-      </c>
-      <c r="D13" s="89" t="s">
-        <v>180</v>
-      </c>
-      <c r="E13" s="89"/>
-      <c r="F13" s="89"/>
-      <c r="G13" s="89"/>
-      <c r="H13" s="89"/>
-      <c r="I13" s="90"/>
+        <v>119</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="125" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="125"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="126"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:12" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B14" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" s="89" t="s">
-        <v>182</v>
-      </c>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="90"/>
+        <v>120</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" s="125" t="s">
+        <v>172</v>
+      </c>
+      <c r="E14" s="125"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="126"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:12" s="114" customFormat="1" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" s="82" customFormat="1" ht="22.5" x14ac:dyDescent="0.2">
       <c r="B15" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="89" t="s">
-        <v>183</v>
-      </c>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="90"/>
+        <v>122</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="125" t="s">
+        <v>173</v>
+      </c>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="126"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
     </row>
-    <row r="16" spans="1:12" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B16" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="89" t="s">
-        <v>184</v>
-      </c>
-      <c r="E16" s="89"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="89"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="90"/>
+        <v>124</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="125" t="s">
+        <v>174</v>
+      </c>
+      <c r="E16" s="125"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="125"/>
+      <c r="I16" s="126"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B17" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="C17" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="D17" s="89" t="s">
-        <v>185</v>
-      </c>
-      <c r="E17" s="89"/>
-      <c r="F17" s="89"/>
-      <c r="G17" s="89"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="90"/>
+        <v>126</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" s="125" t="s">
+        <v>175</v>
+      </c>
+      <c r="E17" s="125"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="126"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B18" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="D18" s="89" t="s">
-        <v>186</v>
-      </c>
-      <c r="E18" s="89"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="89"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="90"/>
+        <v>128</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="125" t="s">
+        <v>176</v>
+      </c>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="126"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="2:11" s="114" customFormat="1" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" s="82" customFormat="1" ht="22.5" x14ac:dyDescent="0.2">
       <c r="B19" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="C19" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="D19" s="89" t="s">
-        <v>187</v>
-      </c>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="90"/>
+        <v>130</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="125" t="s">
+        <v>177</v>
+      </c>
+      <c r="E19" s="125"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="126"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B20" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="C20" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="89" t="s">
-        <v>188</v>
-      </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="90"/>
+        <v>132</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="125" t="s">
+        <v>178</v>
+      </c>
+      <c r="E20" s="125"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="125"/>
+      <c r="I20" s="126"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B21" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="C21" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="D21" s="89" t="s">
-        <v>189</v>
-      </c>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="90"/>
+        <v>134</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="125" t="s">
+        <v>179</v>
+      </c>
+      <c r="E21" s="125"/>
+      <c r="F21" s="125"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="125"/>
+      <c r="I21" s="126"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
     </row>
-    <row r="22" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B22" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="C22" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="D22" s="89" t="s">
-        <v>190</v>
-      </c>
-      <c r="E22" s="89"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="89"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="90"/>
+        <v>136</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="125" t="s">
+        <v>180</v>
+      </c>
+      <c r="E22" s="125"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="125"/>
+      <c r="I22" s="126"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
     </row>
-    <row r="23" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B23" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="C23" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="D23" s="89" t="s">
-        <v>191</v>
-      </c>
-      <c r="E23" s="89"/>
-      <c r="F23" s="89"/>
-      <c r="G23" s="89"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="90"/>
+        <v>138</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="125" t="s">
+        <v>181</v>
+      </c>
+      <c r="E23" s="125"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="126"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
     </row>
-    <row r="24" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" s="82" customFormat="1" ht="45" x14ac:dyDescent="0.2">
       <c r="B24" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="C24" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="D24" s="89" t="s">
-        <v>192</v>
-      </c>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="90"/>
+        <v>140</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>465</v>
+      </c>
+      <c r="D24" s="125" t="s">
+        <v>466</v>
+      </c>
+      <c r="E24" s="125"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="126"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
     </row>
-    <row r="25" spans="2:11" s="114" customFormat="1" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" s="82" customFormat="1" ht="45" x14ac:dyDescent="0.2">
       <c r="B25" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="C25" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="D25" s="89" t="s">
-        <v>193</v>
-      </c>
-      <c r="E25" s="89"/>
-      <c r="F25" s="89"/>
-      <c r="G25" s="89"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="90"/>
+        <v>141</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>467</v>
+      </c>
+      <c r="D25" s="125" t="s">
+        <v>468</v>
+      </c>
+      <c r="E25" s="125"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="125"/>
+      <c r="I25" s="126"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
     </row>
-    <row r="26" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B26" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="C26" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="D26" s="108" t="s">
-        <v>194</v>
-      </c>
-      <c r="E26" s="109"/>
-      <c r="F26" s="109"/>
-      <c r="G26" s="109"/>
-      <c r="H26" s="109"/>
-      <c r="I26" s="110"/>
+        <v>142</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="109" t="s">
+        <v>182</v>
+      </c>
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="111"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
     </row>
-    <row r="27" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B27" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="C27" s="42" t="s">
-        <v>154</v>
-      </c>
-      <c r="D27" s="108" t="s">
-        <v>195</v>
-      </c>
-      <c r="E27" s="109"/>
-      <c r="F27" s="109"/>
-      <c r="G27" s="109"/>
-      <c r="H27" s="109"/>
-      <c r="I27" s="110"/>
+        <v>144</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" s="109" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" s="110"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="111"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
     </row>
-    <row r="28" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B28" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C28" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" s="108" t="s">
-        <v>196</v>
-      </c>
-      <c r="E28" s="109"/>
-      <c r="F28" s="109"/>
-      <c r="G28" s="109"/>
-      <c r="H28" s="109"/>
-      <c r="I28" s="110"/>
+        <v>146</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="109" t="s">
+        <v>184</v>
+      </c>
+      <c r="E28" s="110"/>
+      <c r="F28" s="110"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="111"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B29" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="C29" s="42" t="s">
-        <v>158</v>
-      </c>
-      <c r="D29" s="108" t="s">
-        <v>197</v>
-      </c>
-      <c r="E29" s="109"/>
-      <c r="F29" s="109"/>
-      <c r="G29" s="109"/>
-      <c r="H29" s="109"/>
-      <c r="I29" s="110"/>
+        <v>148</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" s="109" t="s">
+        <v>185</v>
+      </c>
+      <c r="E29" s="110"/>
+      <c r="F29" s="110"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="111"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
     </row>
-    <row r="30" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B30" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="C30" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="D30" s="108" t="s">
-        <v>198</v>
-      </c>
-      <c r="E30" s="109"/>
-      <c r="F30" s="109"/>
-      <c r="G30" s="109"/>
-      <c r="H30" s="109"/>
-      <c r="I30" s="110"/>
+        <v>150</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="D30" s="109" t="s">
+        <v>186</v>
+      </c>
+      <c r="E30" s="110"/>
+      <c r="F30" s="110"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="111"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
     </row>
-    <row r="31" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B31" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="C31" s="42" t="s">
-        <v>162</v>
-      </c>
-      <c r="D31" s="108" t="s">
-        <v>199</v>
-      </c>
-      <c r="E31" s="109"/>
-      <c r="F31" s="109"/>
-      <c r="G31" s="109"/>
-      <c r="H31" s="109"/>
-      <c r="I31" s="110"/>
+        <v>152</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="109" t="s">
+        <v>187</v>
+      </c>
+      <c r="E31" s="110"/>
+      <c r="F31" s="110"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="110"/>
+      <c r="I31" s="111"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
     </row>
-    <row r="32" spans="2:11" s="114" customFormat="1" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" s="82" customFormat="1" ht="22.5" x14ac:dyDescent="0.2">
       <c r="B32" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="C32" s="42" t="s">
-        <v>164</v>
-      </c>
-      <c r="D32" s="108" t="s">
-        <v>200</v>
-      </c>
-      <c r="E32" s="109"/>
-      <c r="F32" s="109"/>
-      <c r="G32" s="109"/>
-      <c r="H32" s="109"/>
-      <c r="I32" s="110"/>
+        <v>154</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="D32" s="109" t="s">
+        <v>188</v>
+      </c>
+      <c r="E32" s="110"/>
+      <c r="F32" s="110"/>
+      <c r="G32" s="110"/>
+      <c r="H32" s="110"/>
+      <c r="I32" s="111"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
     </row>
-    <row r="33" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B33" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="C33" s="42" t="s">
-        <v>166</v>
-      </c>
-      <c r="D33" s="108" t="s">
-        <v>201</v>
-      </c>
-      <c r="E33" s="109"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="109"/>
-      <c r="H33" s="109"/>
-      <c r="I33" s="110"/>
+        <v>156</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="D33" s="109" t="s">
+        <v>189</v>
+      </c>
+      <c r="E33" s="110"/>
+      <c r="F33" s="110"/>
+      <c r="G33" s="110"/>
+      <c r="H33" s="110"/>
+      <c r="I33" s="111"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
     </row>
-    <row r="34" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B34" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>168</v>
-      </c>
-      <c r="D34" s="89" t="s">
-        <v>202</v>
-      </c>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="89"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="90"/>
+        <v>158</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" s="125" t="s">
+        <v>190</v>
+      </c>
+      <c r="E34" s="125"/>
+      <c r="F34" s="125"/>
+      <c r="G34" s="125"/>
+      <c r="H34" s="125"/>
+      <c r="I34" s="126"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
     </row>
-    <row r="35" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B35" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>170</v>
-      </c>
-      <c r="D35" s="89" t="s">
-        <v>203</v>
-      </c>
-      <c r="E35" s="89"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="89"/>
-      <c r="H35" s="89"/>
-      <c r="I35" s="90"/>
+        <v>160</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" s="125" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" s="125"/>
+      <c r="F35" s="125"/>
+      <c r="G35" s="125"/>
+      <c r="H35" s="125"/>
+      <c r="I35" s="126"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
     </row>
-    <row r="36" spans="2:11" s="114" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:11" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B36" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="C36" s="42" t="s">
-        <v>172</v>
-      </c>
-      <c r="D36" s="89" t="s">
-        <v>204</v>
-      </c>
-      <c r="E36" s="89"/>
-      <c r="F36" s="89"/>
-      <c r="G36" s="89"/>
-      <c r="H36" s="89"/>
-      <c r="I36" s="90"/>
+        <v>162</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="125" t="s">
+        <v>192</v>
+      </c>
+      <c r="E36" s="125"/>
+      <c r="F36" s="125"/>
+      <c r="G36" s="125"/>
+      <c r="H36" s="125"/>
+      <c r="I36" s="126"/>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
     </row>
-    <row r="37" spans="2:11" s="114" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:11" s="82" customFormat="1" ht="45" x14ac:dyDescent="0.2">
       <c r="B37" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="C37" s="42" t="s">
-        <v>174</v>
-      </c>
-      <c r="D37" s="89" t="s">
-        <v>205</v>
-      </c>
-      <c r="E37" s="89"/>
-      <c r="F37" s="89"/>
-      <c r="G37" s="89"/>
-      <c r="H37" s="89"/>
-      <c r="I37" s="90"/>
+        <v>164</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="D37" s="125" t="s">
+        <v>193</v>
+      </c>
+      <c r="E37" s="125"/>
+      <c r="F37" s="125"/>
+      <c r="G37" s="125"/>
+      <c r="H37" s="125"/>
+      <c r="I37" s="126"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
     </row>
-    <row r="38" spans="2:11" s="114" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="37"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="91"/>
-      <c r="E38" s="91"/>
-      <c r="F38" s="91"/>
-      <c r="G38" s="91"/>
-      <c r="H38" s="91"/>
-      <c r="I38" s="92"/>
+    <row r="38" spans="2:11" s="82" customFormat="1" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="37" t="s">
+        <v>469</v>
+      </c>
+      <c r="C38" s="49" t="s">
+        <v>470</v>
+      </c>
+      <c r="D38" s="127" t="s">
+        <v>471</v>
+      </c>
+      <c r="E38" s="127"/>
+      <c r="F38" s="127"/>
+      <c r="G38" s="127"/>
+      <c r="H38" s="127"/>
+      <c r="I38" s="128"/>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
     </row>
-    <row r="39" spans="2:11" s="114" customFormat="1" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="C39" s="129"/>
-    </row>
-    <row r="40" spans="2:11" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C40" s="129"/>
-    </row>
-    <row r="41" spans="2:11" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C41" s="129"/>
-    </row>
-    <row r="42" spans="2:11" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C42" s="129"/>
-    </row>
-    <row r="43" spans="2:11" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C43" s="129"/>
-    </row>
-    <row r="44" spans="2:11" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C44" s="129"/>
-    </row>
-    <row r="45" spans="2:11" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C45" s="129"/>
-    </row>
-    <row r="46" spans="2:11" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C46" s="129"/>
-    </row>
-    <row r="47" spans="2:11" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C47" s="129"/>
-    </row>
-    <row r="48" spans="2:11" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C48" s="129"/>
-    </row>
-    <row r="49" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C49" s="129"/>
-    </row>
-    <row r="50" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C50" s="129"/>
-    </row>
-    <row r="51" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C51" s="129"/>
-    </row>
-    <row r="52" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C52" s="129"/>
-    </row>
-    <row r="53" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C53" s="129"/>
-    </row>
-    <row r="54" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C54" s="129"/>
-    </row>
-    <row r="55" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C55" s="129"/>
-    </row>
-    <row r="56" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C56" s="129"/>
-    </row>
-    <row r="57" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C57" s="129"/>
-    </row>
-    <row r="58" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C58" s="129"/>
-    </row>
-    <row r="59" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C59" s="129"/>
-    </row>
-    <row r="60" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C60" s="129"/>
-    </row>
-    <row r="61" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C61" s="129"/>
-    </row>
-    <row r="62" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C62" s="129"/>
-    </row>
-    <row r="63" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C63" s="129"/>
-    </row>
-    <row r="64" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C64" s="129"/>
-    </row>
-    <row r="65" spans="3:3" s="114" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C65" s="129"/>
+    <row r="39" spans="2:11" s="82" customFormat="1" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C39" s="91"/>
+    </row>
+    <row r="40" spans="2:11" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C40" s="91"/>
+    </row>
+    <row r="41" spans="2:11" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C41" s="91"/>
+    </row>
+    <row r="42" spans="2:11" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C42" s="91"/>
+    </row>
+    <row r="43" spans="2:11" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C43" s="91"/>
+    </row>
+    <row r="44" spans="2:11" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C44" s="91"/>
+    </row>
+    <row r="45" spans="2:11" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C45" s="91"/>
+    </row>
+    <row r="46" spans="2:11" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C46" s="91"/>
+    </row>
+    <row r="47" spans="2:11" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C47" s="91"/>
+    </row>
+    <row r="48" spans="2:11" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C48" s="91"/>
+    </row>
+    <row r="49" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C49" s="91"/>
+    </row>
+    <row r="50" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C50" s="91"/>
+    </row>
+    <row r="51" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C51" s="91"/>
+    </row>
+    <row r="52" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C52" s="91"/>
+    </row>
+    <row r="53" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C53" s="91"/>
+    </row>
+    <row r="54" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C54" s="91"/>
+    </row>
+    <row r="55" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C55" s="91"/>
+    </row>
+    <row r="56" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C56" s="91"/>
+    </row>
+    <row r="57" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C57" s="91"/>
+    </row>
+    <row r="58" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C58" s="91"/>
+    </row>
+    <row r="59" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C59" s="91"/>
+    </row>
+    <row r="60" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C60" s="91"/>
+    </row>
+    <row r="61" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C61" s="91"/>
+    </row>
+    <row r="62" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C62" s="91"/>
+    </row>
+    <row r="63" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C63" s="91"/>
+    </row>
+    <row r="64" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C64" s="91"/>
+    </row>
+    <row r="65" spans="3:3" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C65" s="91"/>
     </row>
     <row r="66" spans="3:3" x14ac:dyDescent="0.2"/>
     <row r="67" spans="3:3" x14ac:dyDescent="0.2"/>
@@ -6127,31 +6231,6 @@
     <row r="97" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="D28:I28"/>
-    <mergeCell ref="D29:I29"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="D24:I24"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="D18:I18"/>
     <mergeCell ref="D38:I38"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="D34:I34"/>
@@ -6163,6 +6242,31 @@
     <mergeCell ref="D21:I21"/>
     <mergeCell ref="D22:I22"/>
     <mergeCell ref="D23:I23"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="D30:I30"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8:C38" xr:uid="{33980737-BF5A-45C5-9FE7-D8B9848E53F2}">
@@ -6189,7 +6293,7 @@
     <col min="4" max="4" width="22.28515625" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="55" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="54" customWidth="1"/>
     <col min="8" max="8" width="53.5703125" customWidth="1"/>
     <col min="9" max="9" width="21.140625" customWidth="1"/>
     <col min="10" max="10" width="25.5703125" customWidth="1"/>
@@ -6200,34 +6304,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="70"/>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
+      <c r="A1" s="69"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="26.25" x14ac:dyDescent="0.2">
-      <c r="A2" s="70"/>
-      <c r="B2" s="76" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="70"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="69"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
@@ -6236,7 +6340,7 @@
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="69"/>
+      <c r="G3" s="68"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
@@ -6245,50 +6349,50 @@
     </row>
     <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="130" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="95"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="59" t="s">
+      <c r="D5" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="59" t="s">
+      <c r="E5" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="F5" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="59" t="s">
+      <c r="G5" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="58" t="s">
+      <c r="H5" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="58" t="s">
+      <c r="I5" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="59" t="s">
+      <c r="J5" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="60" t="s">
+      <c r="K5" s="59" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="6"/>
@@ -6298,7 +6402,7 @@
       <c r="B6" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="52" t="s">
         <v>39</v>
       </c>
       <c r="D6" s="30" t="s">
@@ -6307,7 +6411,7 @@
       <c r="E6" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="56" t="s">
+      <c r="F6" s="55" t="s">
         <v>44</v>
       </c>
       <c r="G6" s="30" t="s">
@@ -6322,7 +6426,7 @@
       <c r="J6" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="54" t="s">
+      <c r="K6" s="53" t="s">
         <v>47</v>
       </c>
       <c r="L6" s="6"/>
@@ -6330,1703 +6434,1787 @@
     <row r="7" spans="1:12" ht="43.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>207</v>
+        <v>194</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>195</v>
       </c>
       <c r="D7" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="40" t="s">
-        <v>208</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="G7" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>211</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="J7" s="40" t="s">
-        <v>213</v>
-      </c>
-      <c r="K7" s="41" t="s">
-        <v>214</v>
+      <c r="E7" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="F7" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="G7" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="H7" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="I7" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="J7" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="K7" s="40" t="s">
+        <v>202</v>
       </c>
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="33" t="s">
-        <v>215</v>
-      </c>
-      <c r="C8" s="42" t="s">
-        <v>216</v>
+        <v>203</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>204</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="E8" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="H8" s="42" t="s">
+        <v>206</v>
+      </c>
+      <c r="I8" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="J8" s="42" t="s">
+        <v>207</v>
+      </c>
+      <c r="K8" s="43" t="s">
         <v>208</v>
-      </c>
-      <c r="F8" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="G8" s="43" t="s">
-        <v>210</v>
-      </c>
-      <c r="H8" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="I8" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="J8" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="K8" s="44" t="s">
-        <v>220</v>
       </c>
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>222</v>
+        <v>209</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>210</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>223</v>
-      </c>
-      <c r="E9" s="43" t="s">
-        <v>208</v>
-      </c>
-      <c r="F9" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="G9" s="43" t="s">
-        <v>210</v>
-      </c>
-      <c r="H9" s="43" t="s">
-        <v>224</v>
-      </c>
-      <c r="I9" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="H9" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="J9" s="43" t="s">
-        <v>225</v>
-      </c>
-      <c r="K9" s="44" t="s">
-        <v>226</v>
+      <c r="I9" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="J9" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>214</v>
       </c>
       <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>228</v>
+        <v>215</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>216</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>229</v>
-      </c>
-      <c r="E10" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="F10" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="F10" s="43" t="s">
-        <v>220</v>
-      </c>
-      <c r="G10" s="43" t="s">
-        <v>210</v>
-      </c>
-      <c r="H10" s="43" t="s">
-        <v>230</v>
-      </c>
-      <c r="I10" s="43" t="s">
-        <v>231</v>
-      </c>
-      <c r="J10" s="43" t="s">
-        <v>225</v>
-      </c>
-      <c r="K10" s="44" t="s">
-        <v>220</v>
+      <c r="G10" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="I10" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="J10" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K10" s="43" t="s">
+        <v>208</v>
       </c>
       <c r="L10" s="6"/>
     </row>
     <row r="11" spans="1:12" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>233</v>
+        <v>220</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>221</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="E11" s="43" t="s">
-        <v>235</v>
-      </c>
-      <c r="F11" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="G11" s="43" t="s">
-        <v>236</v>
-      </c>
-      <c r="H11" s="43" t="s">
-        <v>237</v>
-      </c>
-      <c r="I11" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="J11" s="43" t="s">
-        <v>238</v>
-      </c>
-      <c r="K11" s="44" t="s">
-        <v>220</v>
+        <v>222</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>224</v>
+      </c>
+      <c r="H11" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="I11" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="J11" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>208</v>
       </c>
       <c r="L11" s="6"/>
     </row>
     <row r="12" spans="1:12" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>240</v>
+        <v>227</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>228</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="G12" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="H12" s="45" t="s">
-        <v>242</v>
-      </c>
-      <c r="I12" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="J12" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="K12" s="46" t="s">
-        <v>220</v>
+        <v>229</v>
+      </c>
+      <c r="E12" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F12" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="G12" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>230</v>
+      </c>
+      <c r="I12" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="J12" s="44" t="s">
+        <v>231</v>
+      </c>
+      <c r="K12" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L12" s="6"/>
     </row>
     <row r="13" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>245</v>
+        <v>232</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>233</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="E13" s="45" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F13" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H13" s="44" t="s">
         <v>235</v>
       </c>
-      <c r="F13" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="G13" s="45" t="s">
+      <c r="I13" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="J13" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="H13" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="I13" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="J13" s="45" t="s">
-        <v>248</v>
-      </c>
-      <c r="K13" s="46" t="s">
-        <v>220</v>
+      <c r="K13" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L13" s="6"/>
     </row>
     <row r="14" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
       <c r="B14" s="33" t="s">
-        <v>249</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>250</v>
+        <v>237</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>238</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F14" s="45" t="s">
-        <v>252</v>
-      </c>
-      <c r="G14" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="H14" s="45" t="s">
-        <v>253</v>
-      </c>
-      <c r="I14" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="J14" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="K14" s="46" t="s">
-        <v>255</v>
+        <v>239</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F14" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="I14" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>242</v>
+      </c>
+      <c r="K14" s="45" t="s">
+        <v>243</v>
       </c>
       <c r="L14" s="6"/>
     </row>
     <row r="15" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="C15" s="42" t="s">
-        <v>257</v>
+        <v>244</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>245</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F15" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="G15" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="H15" s="45" t="s">
-        <v>218</v>
-      </c>
-      <c r="I15" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="J15" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="K15" s="46" t="s">
-        <v>220</v>
+        <v>246</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="I15" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="J15" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="K15" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L15" s="6"/>
     </row>
     <row r="16" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="35" t="s">
-        <v>260</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>261</v>
+        <v>248</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>249</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>262</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>235</v>
-      </c>
-      <c r="F16" s="48" t="s">
-        <v>209</v>
-      </c>
-      <c r="G16" s="48" t="s">
-        <v>236</v>
-      </c>
-      <c r="H16" s="48" t="s">
-        <v>218</v>
-      </c>
-      <c r="I16" s="48" t="s">
-        <v>212</v>
-      </c>
-      <c r="J16" s="48" t="s">
-        <v>219</v>
-      </c>
-      <c r="K16" s="49" t="s">
-        <v>220</v>
+        <v>250</v>
+      </c>
+      <c r="E16" s="47" t="s">
+        <v>223</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="G16" s="47" t="s">
+        <v>224</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="I16" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="J16" s="47" t="s">
+        <v>207</v>
+      </c>
+      <c r="K16" s="48" t="s">
+        <v>208</v>
       </c>
       <c r="L16" s="6"/>
     </row>
     <row r="17" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="C17" s="42" t="s">
-        <v>264</v>
+        <v>251</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>252</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>265</v>
-      </c>
-      <c r="E17" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F17" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="G17" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="H17" s="45" t="s">
-        <v>266</v>
-      </c>
-      <c r="I17" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="J17" s="45" t="s">
-        <v>219</v>
-      </c>
-      <c r="K17" s="46" t="s">
-        <v>220</v>
+        <v>253</v>
+      </c>
+      <c r="E17" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H17" s="44" t="s">
+        <v>254</v>
+      </c>
+      <c r="I17" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="J17" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="K17" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L17" s="6"/>
     </row>
     <row r="18" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
       <c r="B18" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="C18" s="42" t="s">
-        <v>268</v>
+        <v>255</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>256</v>
       </c>
       <c r="D18" s="34" t="s">
-        <v>269</v>
-      </c>
-      <c r="E18" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="F18" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="G18" s="45" t="s">
-        <v>210</v>
-      </c>
-      <c r="H18" s="45" t="s">
-        <v>270</v>
-      </c>
-      <c r="I18" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="J18" s="45" t="s">
-        <v>271</v>
-      </c>
-      <c r="K18" s="46" t="s">
-        <v>272</v>
+        <v>257</v>
+      </c>
+      <c r="E18" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F18" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="H18" s="44" t="s">
+        <v>258</v>
+      </c>
+      <c r="I18" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="J18" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="K18" s="45" t="s">
+        <v>260</v>
       </c>
       <c r="L18" s="6"/>
     </row>
     <row r="19" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
       <c r="B19" s="33" t="s">
-        <v>273</v>
-      </c>
-      <c r="C19" s="42" t="s">
-        <v>274</v>
+        <v>261</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>262</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>275</v>
-      </c>
-      <c r="E19" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F19" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="G19" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="H19" s="45" t="s">
-        <v>276</v>
-      </c>
-      <c r="I19" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="J19" s="45" t="s">
-        <v>271</v>
-      </c>
-      <c r="K19" s="46" t="s">
-        <v>220</v>
+        <v>263</v>
+      </c>
+      <c r="E19" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F19" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H19" s="44" t="s">
+        <v>264</v>
+      </c>
+      <c r="I19" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="J19" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="K19" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L19" s="6"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="C20" s="42" t="s">
-        <v>278</v>
+        <v>265</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>266</v>
       </c>
       <c r="D20" s="34" t="s">
-        <v>279</v>
-      </c>
-      <c r="E20" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F20" s="45" t="s">
-        <v>277</v>
-      </c>
-      <c r="G20" s="45" t="s">
-        <v>280</v>
-      </c>
-      <c r="H20" s="45" t="s">
-        <v>281</v>
-      </c>
-      <c r="I20" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="J20" s="45" t="s">
-        <v>283</v>
-      </c>
-      <c r="K20" s="46" t="s">
-        <v>220</v>
+        <v>267</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F20" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="H20" s="44" t="s">
+        <v>269</v>
+      </c>
+      <c r="I20" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="J20" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="K20" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L20" s="6"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="C21" s="42" t="s">
-        <v>285</v>
+        <v>272</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>273</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>286</v>
-      </c>
-      <c r="E21" s="45" t="s">
+        <v>274</v>
+      </c>
+      <c r="E21" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="45" t="s">
+      <c r="F21" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="45" t="s">
-        <v>210</v>
-      </c>
-      <c r="H21" s="45" t="s">
-        <v>287</v>
-      </c>
-      <c r="I21" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="J21" s="45" t="s">
-        <v>219</v>
-      </c>
-      <c r="K21" s="46" t="s">
-        <v>220</v>
+      <c r="G21" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="H21" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="I21" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="J21" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="K21" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L21" s="6"/>
     </row>
     <row r="22" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
       <c r="B22" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="C22" s="47" t="s">
-        <v>289</v>
+        <v>276</v>
+      </c>
+      <c r="C22" s="46" t="s">
+        <v>277</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>290</v>
-      </c>
-      <c r="E22" s="48" t="s">
+        <v>278</v>
+      </c>
+      <c r="E22" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="F22" s="48" t="s">
+      <c r="F22" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="48" t="s">
-        <v>210</v>
-      </c>
-      <c r="H22" s="48" t="s">
-        <v>291</v>
-      </c>
-      <c r="I22" s="48" t="s">
-        <v>212</v>
-      </c>
-      <c r="J22" s="48" t="s">
-        <v>292</v>
-      </c>
-      <c r="K22" s="49" t="s">
-        <v>220</v>
+      <c r="G22" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="H22" s="47" t="s">
+        <v>279</v>
+      </c>
+      <c r="I22" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="J22" s="47" t="s">
+        <v>280</v>
+      </c>
+      <c r="K22" s="48" t="s">
+        <v>208</v>
       </c>
       <c r="L22" s="6"/>
     </row>
     <row r="23" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
       <c r="B23" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="C23" s="42" t="s">
-        <v>294</v>
+        <v>281</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>282</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>295</v>
-      </c>
-      <c r="E23" s="45" t="s">
+        <v>283</v>
+      </c>
+      <c r="E23" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F23" s="45" t="s">
-        <v>296</v>
-      </c>
-      <c r="G23" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="H23" s="45" t="s">
-        <v>474</v>
-      </c>
-      <c r="I23" s="45" t="s">
-        <v>297</v>
-      </c>
-      <c r="J23" s="45" t="s">
-        <v>298</v>
-      </c>
-      <c r="K23" s="46" t="s">
-        <v>299</v>
+      <c r="F23" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H23" s="44" t="s">
+        <v>452</v>
+      </c>
+      <c r="I23" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="J23" s="44" t="s">
+        <v>286</v>
+      </c>
+      <c r="K23" s="45" t="s">
+        <v>287</v>
       </c>
       <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A24" s="6"/>
       <c r="B24" s="33" t="s">
-        <v>300</v>
-      </c>
-      <c r="C24" s="42" t="s">
-        <v>475</v>
+        <v>288</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>453</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="E24" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="F24" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="G24" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="H24" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="I24" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="J24" s="45" t="s">
-        <v>303</v>
-      </c>
-      <c r="K24" s="46" t="s">
-        <v>304</v>
+        <v>289</v>
+      </c>
+      <c r="E24" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F24" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="G24" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H24" s="44" t="s">
+        <v>290</v>
+      </c>
+      <c r="I24" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="J24" s="44" t="s">
+        <v>291</v>
+      </c>
+      <c r="K24" s="45" t="s">
+        <v>292</v>
       </c>
       <c r="L24" s="6"/>
     </row>
     <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="33" t="s">
-        <v>305</v>
-      </c>
-      <c r="C25" s="42" t="s">
-        <v>306</v>
+        <v>293</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>294</v>
       </c>
       <c r="D25" s="34" t="s">
-        <v>307</v>
-      </c>
-      <c r="E25" s="45" t="s">
+        <v>295</v>
+      </c>
+      <c r="E25" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F25" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="G25" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H25" s="44" t="s">
+        <v>296</v>
+      </c>
+      <c r="I25" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="J25" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="K25" s="45" t="s">
         <v>208</v>
-      </c>
-      <c r="F25" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="G25" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="H25" s="45" t="s">
-        <v>308</v>
-      </c>
-      <c r="I25" s="45" t="s">
-        <v>309</v>
-      </c>
-      <c r="J25" s="45" t="s">
-        <v>271</v>
-      </c>
-      <c r="K25" s="46" t="s">
-        <v>220</v>
       </c>
       <c r="L25" s="6"/>
     </row>
     <row r="26" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="C26" s="42" t="s">
-        <v>311</v>
+        <v>298</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>299</v>
       </c>
       <c r="D26" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="E26" s="45" t="s">
+        <v>300</v>
+      </c>
+      <c r="E26" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F26" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="G26" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H26" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="I26" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="J26" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="K26" s="45" t="s">
         <v>208</v>
-      </c>
-      <c r="F26" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="G26" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="H26" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="I26" s="45" t="s">
-        <v>309</v>
-      </c>
-      <c r="J26" s="45" t="s">
-        <v>271</v>
-      </c>
-      <c r="K26" s="46" t="s">
-        <v>220</v>
       </c>
       <c r="L26" s="6"/>
     </row>
     <row r="27" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="33" t="s">
-        <v>314</v>
-      </c>
-      <c r="C27" s="42" t="s">
-        <v>315</v>
+        <v>302</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>303</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>316</v>
-      </c>
-      <c r="E27" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F27" s="45" t="s">
-        <v>317</v>
-      </c>
-      <c r="G27" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="H27" s="45" t="s">
-        <v>318</v>
-      </c>
-      <c r="I27" s="45" t="s">
-        <v>309</v>
-      </c>
-      <c r="J27" s="45" t="s">
-        <v>271</v>
-      </c>
-      <c r="K27" s="46" t="s">
-        <v>220</v>
+        <v>304</v>
+      </c>
+      <c r="E27" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F27" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="G27" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H27" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="I27" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="J27" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="K27" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L27" s="6"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="B28" s="33" t="s">
-        <v>319</v>
-      </c>
-      <c r="C28" s="42" t="s">
-        <v>320</v>
+        <v>307</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>308</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>321</v>
-      </c>
-      <c r="E28" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F28" s="45" t="s">
-        <v>322</v>
-      </c>
-      <c r="G28" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="H28" s="45" t="s">
-        <v>323</v>
-      </c>
-      <c r="I28" s="45" t="s">
         <v>309</v>
       </c>
-      <c r="J28" s="45" t="s">
-        <v>324</v>
-      </c>
-      <c r="K28" s="46" t="s">
-        <v>325</v>
+      <c r="E28" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F28" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="G28" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H28" s="44" t="s">
+        <v>311</v>
+      </c>
+      <c r="I28" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="J28" s="44" t="s">
+        <v>312</v>
+      </c>
+      <c r="K28" s="45" t="s">
+        <v>313</v>
       </c>
       <c r="L28" s="6"/>
     </row>
     <row r="29" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="33" t="s">
-        <v>326</v>
-      </c>
-      <c r="C29" s="42" t="s">
-        <v>327</v>
+        <v>314</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>315</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="E29" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="F29" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="G29" s="45" t="s">
-        <v>329</v>
-      </c>
-      <c r="H29" s="45" t="s">
-        <v>330</v>
-      </c>
-      <c r="I29" s="45" t="s">
-        <v>331</v>
-      </c>
-      <c r="J29" s="45" t="s">
-        <v>332</v>
-      </c>
-      <c r="K29" s="46" t="s">
-        <v>333</v>
+        <v>316</v>
+      </c>
+      <c r="E29" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F29" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="G29" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="H29" s="44" t="s">
+        <v>318</v>
+      </c>
+      <c r="I29" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="J29" s="44" t="s">
+        <v>320</v>
+      </c>
+      <c r="K29" s="45" t="s">
+        <v>321</v>
       </c>
       <c r="L29" s="6"/>
     </row>
     <row r="30" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="B30" s="33" t="s">
-        <v>334</v>
-      </c>
-      <c r="C30" s="42" t="s">
-        <v>335</v>
+        <v>322</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>323</v>
       </c>
       <c r="D30" s="34" t="s">
-        <v>336</v>
-      </c>
-      <c r="E30" s="45" t="s">
+        <v>324</v>
+      </c>
+      <c r="E30" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F30" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="G30" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="H30" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="I30" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="J30" s="44" t="s">
+        <v>327</v>
+      </c>
+      <c r="K30" s="45" t="s">
         <v>208</v>
-      </c>
-      <c r="F30" s="45" t="s">
-        <v>337</v>
-      </c>
-      <c r="G30" s="45" t="s">
-        <v>329</v>
-      </c>
-      <c r="H30" s="45" t="s">
-        <v>338</v>
-      </c>
-      <c r="I30" s="45" t="s">
-        <v>331</v>
-      </c>
-      <c r="J30" s="45" t="s">
-        <v>339</v>
-      </c>
-      <c r="K30" s="46" t="s">
-        <v>220</v>
       </c>
       <c r="L30" s="6"/>
     </row>
     <row r="31" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A31" s="6"/>
       <c r="B31" s="33" t="s">
-        <v>340</v>
-      </c>
-      <c r="C31" s="42" t="s">
-        <v>341</v>
+        <v>328</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>329</v>
       </c>
       <c r="D31" s="34" t="s">
-        <v>342</v>
-      </c>
-      <c r="E31" s="45" t="s">
+        <v>330</v>
+      </c>
+      <c r="E31" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F31" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="G31" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="H31" s="44" t="s">
+        <v>331</v>
+      </c>
+      <c r="I31" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="J31" s="44" t="s">
+        <v>213</v>
+      </c>
+      <c r="K31" s="45" t="s">
         <v>208</v>
-      </c>
-      <c r="F31" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="G31" s="45" t="s">
-        <v>329</v>
-      </c>
-      <c r="H31" s="45" t="s">
-        <v>343</v>
-      </c>
-      <c r="I31" s="45" t="s">
-        <v>231</v>
-      </c>
-      <c r="J31" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="K31" s="46" t="s">
-        <v>220</v>
       </c>
       <c r="L31" s="6"/>
     </row>
     <row r="32" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A32" s="6"/>
       <c r="B32" s="33" t="s">
-        <v>344</v>
-      </c>
-      <c r="C32" s="42" t="s">
-        <v>345</v>
+        <v>332</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>333</v>
       </c>
       <c r="D32" s="34" t="s">
-        <v>346</v>
-      </c>
-      <c r="E32" s="45" t="s">
+        <v>334</v>
+      </c>
+      <c r="E32" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F32" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="F32" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="G32" s="45" t="s">
-        <v>329</v>
-      </c>
-      <c r="H32" s="45" t="s">
-        <v>347</v>
-      </c>
-      <c r="I32" s="45" t="s">
-        <v>231</v>
-      </c>
-      <c r="J32" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="K32" s="46" t="s">
-        <v>220</v>
+      <c r="G32" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="H32" s="44" t="s">
+        <v>335</v>
+      </c>
+      <c r="I32" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="J32" s="44" t="s">
+        <v>213</v>
+      </c>
+      <c r="K32" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L32" s="6"/>
     </row>
     <row r="33" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A33" s="6"/>
       <c r="B33" s="33" t="s">
-        <v>348</v>
-      </c>
-      <c r="C33" s="42" t="s">
-        <v>476</v>
+        <v>336</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>454</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>349</v>
-      </c>
-      <c r="E33" s="45" t="s">
+        <v>337</v>
+      </c>
+      <c r="E33" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F33" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="G33" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="H33" s="44" t="s">
+        <v>339</v>
+      </c>
+      <c r="I33" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="J33" s="44" t="s">
+        <v>341</v>
+      </c>
+      <c r="K33" s="45" t="s">
         <v>208</v>
-      </c>
-      <c r="F33" s="45" t="s">
-        <v>337</v>
-      </c>
-      <c r="G33" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="H33" s="45" t="s">
-        <v>351</v>
-      </c>
-      <c r="I33" s="45" t="s">
-        <v>352</v>
-      </c>
-      <c r="J33" s="45" t="s">
-        <v>353</v>
-      </c>
-      <c r="K33" s="46" t="s">
-        <v>220</v>
       </c>
       <c r="L33" s="6"/>
     </row>
     <row r="34" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A34" s="6"/>
       <c r="B34" s="33" t="s">
-        <v>354</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>355</v>
+        <v>342</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>343</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>356</v>
-      </c>
-      <c r="E34" s="45" t="s">
+        <v>344</v>
+      </c>
+      <c r="E34" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F34" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="G34" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="H34" s="44" t="s">
+        <v>345</v>
+      </c>
+      <c r="I34" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="J34" s="44" t="s">
+        <v>346</v>
+      </c>
+      <c r="K34" s="45" t="s">
         <v>208</v>
-      </c>
-      <c r="F34" s="45" t="s">
-        <v>337</v>
-      </c>
-      <c r="G34" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="H34" s="45" t="s">
-        <v>357</v>
-      </c>
-      <c r="I34" s="45" t="s">
-        <v>352</v>
-      </c>
-      <c r="J34" s="45" t="s">
-        <v>358</v>
-      </c>
-      <c r="K34" s="46" t="s">
-        <v>220</v>
       </c>
       <c r="L34" s="6"/>
     </row>
     <row r="35" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
       <c r="B35" s="33" t="s">
-        <v>359</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>360</v>
+        <v>347</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>348</v>
       </c>
       <c r="D35" s="34" t="s">
-        <v>361</v>
-      </c>
-      <c r="E35" s="45" t="s">
+        <v>349</v>
+      </c>
+      <c r="E35" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F35" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="G35" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="H35" s="44" t="s">
+        <v>345</v>
+      </c>
+      <c r="I35" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="J35" s="44" t="s">
+        <v>341</v>
+      </c>
+      <c r="K35" s="45" t="s">
         <v>208</v>
-      </c>
-      <c r="F35" s="45" t="s">
-        <v>337</v>
-      </c>
-      <c r="G35" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="H35" s="45" t="s">
-        <v>357</v>
-      </c>
-      <c r="I35" s="45" t="s">
-        <v>352</v>
-      </c>
-      <c r="J35" s="45" t="s">
-        <v>353</v>
-      </c>
-      <c r="K35" s="46" t="s">
-        <v>220</v>
       </c>
       <c r="L35" s="6"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="6"/>
       <c r="B36" s="33" t="s">
-        <v>362</v>
-      </c>
-      <c r="C36" s="42" t="s">
-        <v>363</v>
+        <v>350</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>351</v>
       </c>
       <c r="D36" s="34" t="s">
-        <v>364</v>
-      </c>
-      <c r="E36" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F36" s="45" t="s">
-        <v>277</v>
-      </c>
-      <c r="G36" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="H36" s="45" t="s">
-        <v>365</v>
-      </c>
-      <c r="I36" s="45" t="s">
         <v>352</v>
       </c>
-      <c r="J36" s="45" t="s">
+      <c r="E36" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F36" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="G36" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="H36" s="44" t="s">
         <v>353</v>
       </c>
-      <c r="K36" s="46" t="s">
-        <v>220</v>
+      <c r="I36" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="J36" s="44" t="s">
+        <v>341</v>
+      </c>
+      <c r="K36" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L36" s="6"/>
     </row>
-    <row r="37" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
       <c r="B37" s="33" t="s">
-        <v>366</v>
-      </c>
-      <c r="C37" s="42" t="s">
-        <v>367</v>
+        <v>354</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>355</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>368</v>
-      </c>
-      <c r="E37" s="45" t="s">
+        <v>356</v>
+      </c>
+      <c r="E37" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F37" s="45" t="s">
-        <v>369</v>
-      </c>
-      <c r="G37" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="H37" s="45" t="s">
-        <v>370</v>
-      </c>
-      <c r="I37" s="45" t="s">
-        <v>352</v>
-      </c>
-      <c r="J37" s="45" t="s">
-        <v>371</v>
-      </c>
-      <c r="K37" s="46" t="s">
-        <v>372</v>
+      <c r="F37" s="44" t="s">
+        <v>357</v>
+      </c>
+      <c r="G37" s="44" t="s">
+        <v>472</v>
+      </c>
+      <c r="H37" s="44" t="s">
+        <v>473</v>
+      </c>
+      <c r="I37" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="J37" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="K37" s="45" t="s">
+        <v>474</v>
       </c>
       <c r="L37" s="6"/>
     </row>
     <row r="38" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A38" s="6"/>
       <c r="B38" s="33" t="s">
-        <v>373</v>
-      </c>
-      <c r="C38" s="42" t="s">
-        <v>374</v>
+        <v>359</v>
+      </c>
+      <c r="C38" s="41" t="s">
+        <v>360</v>
       </c>
       <c r="D38" s="34" t="s">
-        <v>375</v>
-      </c>
-      <c r="E38" s="45" t="s">
+        <v>361</v>
+      </c>
+      <c r="E38" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F38" s="45" t="s">
-        <v>369</v>
-      </c>
-      <c r="G38" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="H38" s="45" t="s">
-        <v>376</v>
-      </c>
-      <c r="I38" s="45" t="s">
-        <v>352</v>
-      </c>
-      <c r="J38" s="45" t="s">
-        <v>358</v>
-      </c>
-      <c r="K38" s="46" t="s">
-        <v>220</v>
+      <c r="F38" s="44" t="s">
+        <v>357</v>
+      </c>
+      <c r="G38" s="44" t="s">
+        <v>472</v>
+      </c>
+      <c r="H38" s="44" t="s">
+        <v>473</v>
+      </c>
+      <c r="I38" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="J38" s="44" t="s">
+        <v>346</v>
+      </c>
+      <c r="K38" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L38" s="6"/>
     </row>
     <row r="39" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
       <c r="B39" s="33" t="s">
-        <v>377</v>
-      </c>
-      <c r="C39" s="42" t="s">
-        <v>477</v>
+        <v>362</v>
+      </c>
+      <c r="C39" s="41" t="s">
+        <v>455</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>378</v>
-      </c>
-      <c r="E39" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="F39" s="45" t="s">
-        <v>337</v>
-      </c>
-      <c r="G39" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="H39" s="45" t="s">
-        <v>379</v>
-      </c>
-      <c r="I39" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="J39" s="45" t="s">
-        <v>380</v>
-      </c>
-      <c r="K39" s="46" t="s">
-        <v>381</v>
+        <v>363</v>
+      </c>
+      <c r="E39" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="F39" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="G39" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="H39" s="44" t="s">
+        <v>364</v>
+      </c>
+      <c r="I39" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="J39" s="44" t="s">
+        <v>365</v>
+      </c>
+      <c r="K39" s="45" t="s">
+        <v>366</v>
       </c>
       <c r="L39" s="6"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="6"/>
       <c r="B40" s="33" t="s">
-        <v>382</v>
-      </c>
-      <c r="C40" s="42" t="s">
-        <v>383</v>
+        <v>367</v>
+      </c>
+      <c r="C40" s="41" t="s">
+        <v>368</v>
       </c>
       <c r="D40" s="34" t="s">
-        <v>384</v>
-      </c>
-      <c r="E40" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F40" s="45" t="s">
-        <v>385</v>
-      </c>
-      <c r="G40" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="H40" s="45" t="s">
-        <v>386</v>
-      </c>
-      <c r="I40" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="J40" s="45" t="s">
-        <v>380</v>
-      </c>
-      <c r="K40" s="46" t="s">
-        <v>220</v>
+        <v>369</v>
+      </c>
+      <c r="E40" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F40" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="44" t="s">
+        <v>371</v>
+      </c>
+      <c r="I40" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="J40" s="44" t="s">
+        <v>365</v>
+      </c>
+      <c r="K40" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L40" s="6"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="6"/>
       <c r="B41" s="33" t="s">
-        <v>387</v>
-      </c>
-      <c r="C41" s="42" t="s">
-        <v>388</v>
+        <v>372</v>
+      </c>
+      <c r="C41" s="41" t="s">
+        <v>373</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>389</v>
-      </c>
-      <c r="E41" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F41" s="45" t="s">
-        <v>390</v>
-      </c>
-      <c r="G41" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="H41" s="45" t="s">
-        <v>391</v>
-      </c>
-      <c r="I41" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="J41" s="45" t="s">
-        <v>380</v>
-      </c>
-      <c r="K41" s="46" t="s">
-        <v>220</v>
+        <v>374</v>
+      </c>
+      <c r="E41" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F41" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="G41" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="H41" s="44" t="s">
+        <v>376</v>
+      </c>
+      <c r="I41" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="J41" s="44" t="s">
+        <v>365</v>
+      </c>
+      <c r="K41" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L41" s="6"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="6"/>
       <c r="B42" s="33" t="s">
-        <v>392</v>
-      </c>
-      <c r="C42" s="42" t="s">
-        <v>393</v>
+        <v>377</v>
+      </c>
+      <c r="C42" s="41" t="s">
+        <v>378</v>
       </c>
       <c r="D42" s="34" t="s">
-        <v>394</v>
-      </c>
-      <c r="E42" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F42" s="45" t="s">
-        <v>322</v>
-      </c>
-      <c r="G42" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="H42" s="45" t="s">
-        <v>395</v>
-      </c>
-      <c r="I42" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="J42" s="45" t="s">
-        <v>396</v>
-      </c>
-      <c r="K42" s="46" t="s">
-        <v>220</v>
+        <v>379</v>
+      </c>
+      <c r="E42" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F42" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="G42" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="H42" s="44" t="s">
+        <v>380</v>
+      </c>
+      <c r="I42" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="J42" s="44" t="s">
+        <v>381</v>
+      </c>
+      <c r="K42" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L42" s="6"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="6"/>
       <c r="B43" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="C43" s="42" t="s">
-        <v>398</v>
+        <v>382</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>383</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>399</v>
-      </c>
-      <c r="E43" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F43" s="45" t="s">
-        <v>322</v>
-      </c>
-      <c r="G43" s="45" t="s">
-        <v>280</v>
-      </c>
-      <c r="H43" s="45" t="s">
-        <v>400</v>
-      </c>
-      <c r="I43" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="J43" s="45" t="s">
-        <v>401</v>
-      </c>
-      <c r="K43" s="46" t="s">
-        <v>220</v>
+        <v>384</v>
+      </c>
+      <c r="E43" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F43" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="G43" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="H43" s="44" t="s">
+        <v>385</v>
+      </c>
+      <c r="I43" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="J43" s="44" t="s">
+        <v>386</v>
+      </c>
+      <c r="K43" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L43" s="6"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="6"/>
       <c r="B44" s="33" t="s">
-        <v>402</v>
-      </c>
-      <c r="C44" s="42" t="s">
-        <v>403</v>
+        <v>387</v>
+      </c>
+      <c r="C44" s="41" t="s">
+        <v>388</v>
       </c>
       <c r="D44" s="34" t="s">
-        <v>404</v>
-      </c>
-      <c r="E44" s="45" t="s">
+        <v>389</v>
+      </c>
+      <c r="E44" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F44" s="45" t="s">
+      <c r="F44" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="G44" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="H44" s="45" t="s">
-        <v>405</v>
-      </c>
-      <c r="I44" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="J44" s="45" t="s">
-        <v>406</v>
-      </c>
-      <c r="K44" s="46" t="s">
-        <v>220</v>
+      <c r="G44" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="H44" s="44" t="s">
+        <v>390</v>
+      </c>
+      <c r="I44" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="J44" s="44" t="s">
+        <v>391</v>
+      </c>
+      <c r="K44" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L44" s="6"/>
     </row>
     <row r="45" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
       <c r="B45" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="C45" s="42" t="s">
-        <v>408</v>
+        <v>392</v>
+      </c>
+      <c r="C45" s="41" t="s">
+        <v>393</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>409</v>
-      </c>
-      <c r="E45" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="E45" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F45" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="G45" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="H45" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="I45" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="J45" s="45" t="s">
-        <v>412</v>
-      </c>
-      <c r="K45" s="46" t="s">
-        <v>413</v>
+      <c r="F45" s="44" t="s">
+        <v>395</v>
+      </c>
+      <c r="G45" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="H45" s="44" t="s">
+        <v>396</v>
+      </c>
+      <c r="I45" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="J45" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="K45" s="45" t="s">
+        <v>398</v>
       </c>
       <c r="L45" s="6"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
       <c r="B46" s="33" t="s">
-        <v>414</v>
-      </c>
-      <c r="C46" s="42" t="s">
-        <v>415</v>
+        <v>399</v>
+      </c>
+      <c r="C46" s="41" t="s">
+        <v>400</v>
       </c>
       <c r="D46" s="34" t="s">
-        <v>416</v>
-      </c>
-      <c r="E46" s="45" t="s">
+        <v>401</v>
+      </c>
+      <c r="E46" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F46" s="45" t="s">
+      <c r="F46" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="G46" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="H46" s="45" t="s">
-        <v>417</v>
-      </c>
-      <c r="I46" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="J46" s="45" t="s">
-        <v>406</v>
-      </c>
-      <c r="K46" s="46" t="s">
-        <v>418</v>
+      <c r="G46" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="H46" s="44" t="s">
+        <v>402</v>
+      </c>
+      <c r="I46" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="J46" s="44" t="s">
+        <v>391</v>
+      </c>
+      <c r="K46" s="45" t="s">
+        <v>403</v>
       </c>
       <c r="L46" s="6"/>
     </row>
-    <row r="47" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A47" s="6"/>
       <c r="B47" s="33" t="s">
-        <v>419</v>
-      </c>
-      <c r="C47" s="42" t="s">
-        <v>420</v>
+        <v>404</v>
+      </c>
+      <c r="C47" s="41" t="s">
+        <v>480</v>
       </c>
       <c r="D47" s="34" t="s">
-        <v>421</v>
-      </c>
-      <c r="E47" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F47" s="45" t="s">
-        <v>322</v>
-      </c>
-      <c r="G47" s="45" t="s">
-        <v>280</v>
-      </c>
-      <c r="H47" s="45" t="s">
-        <v>422</v>
-      </c>
-      <c r="I47" s="45" t="s">
-        <v>423</v>
-      </c>
-      <c r="J47" s="45" t="s">
-        <v>424</v>
-      </c>
-      <c r="K47" s="46" t="s">
-        <v>220</v>
+        <v>405</v>
+      </c>
+      <c r="E47" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F47" s="44" t="s">
+        <v>481</v>
+      </c>
+      <c r="G47" s="44" t="s">
+        <v>482</v>
+      </c>
+      <c r="H47" s="44" t="s">
+        <v>483</v>
+      </c>
+      <c r="I47" s="44" t="s">
+        <v>406</v>
+      </c>
+      <c r="J47" s="44" t="s">
+        <v>407</v>
+      </c>
+      <c r="K47" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L47" s="6"/>
     </row>
-    <row r="48" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A48" s="6"/>
       <c r="B48" s="33" t="s">
-        <v>425</v>
-      </c>
-      <c r="C48" s="42" t="s">
-        <v>426</v>
+        <v>408</v>
+      </c>
+      <c r="C48" s="41" t="s">
+        <v>409</v>
       </c>
       <c r="D48" s="34" t="s">
-        <v>427</v>
-      </c>
-      <c r="E48" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F48" s="45" t="s">
-        <v>322</v>
-      </c>
-      <c r="G48" s="45" t="s">
-        <v>280</v>
-      </c>
-      <c r="H48" s="45" t="s">
-        <v>428</v>
-      </c>
-      <c r="I48" s="45" t="s">
-        <v>423</v>
-      </c>
-      <c r="J48" s="45" t="s">
-        <v>429</v>
-      </c>
-      <c r="K48" s="46" t="s">
-        <v>220</v>
+        <v>410</v>
+      </c>
+      <c r="E48" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F48" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="G48" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="H48" s="44" t="s">
+        <v>411</v>
+      </c>
+      <c r="I48" s="44" t="s">
+        <v>484</v>
+      </c>
+      <c r="J48" s="44" t="s">
+        <v>412</v>
+      </c>
+      <c r="K48" s="45" t="s">
+        <v>485</v>
       </c>
       <c r="L48" s="6"/>
     </row>
     <row r="49" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
       <c r="B49" s="33" t="s">
-        <v>430</v>
-      </c>
-      <c r="C49" s="42" t="s">
-        <v>431</v>
+        <v>413</v>
+      </c>
+      <c r="C49" s="41" t="s">
+        <v>414</v>
       </c>
       <c r="D49" s="34" t="s">
-        <v>432</v>
-      </c>
-      <c r="E49" s="45" t="s">
+        <v>415</v>
+      </c>
+      <c r="E49" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F49" s="45" t="s">
-        <v>369</v>
-      </c>
-      <c r="G49" s="45" t="s">
-        <v>350</v>
-      </c>
-      <c r="H49" s="45" t="s">
-        <v>433</v>
-      </c>
-      <c r="I49" s="45" t="s">
-        <v>352</v>
-      </c>
-      <c r="J49" s="45" t="s">
-        <v>434</v>
-      </c>
-      <c r="K49" s="46" t="s">
-        <v>435</v>
+      <c r="F49" s="44" t="s">
+        <v>357</v>
+      </c>
+      <c r="G49" s="44" t="s">
+        <v>472</v>
+      </c>
+      <c r="H49" s="44" t="s">
+        <v>416</v>
+      </c>
+      <c r="I49" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="J49" s="44" t="s">
+        <v>417</v>
+      </c>
+      <c r="K49" s="45" t="s">
+        <v>418</v>
       </c>
       <c r="L49" s="6"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="6"/>
       <c r="B50" s="33" t="s">
-        <v>436</v>
-      </c>
-      <c r="C50" s="42" t="s">
-        <v>437</v>
+        <v>419</v>
+      </c>
+      <c r="C50" s="41" t="s">
+        <v>420</v>
       </c>
       <c r="D50" s="34" t="s">
-        <v>438</v>
-      </c>
-      <c r="E50" s="45" t="s">
+        <v>421</v>
+      </c>
+      <c r="E50" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F50" s="45" t="s">
-        <v>439</v>
-      </c>
-      <c r="G50" s="45" t="s">
-        <v>440</v>
-      </c>
-      <c r="H50" s="45" t="s">
-        <v>441</v>
-      </c>
-      <c r="I50" s="45" t="s">
-        <v>442</v>
-      </c>
-      <c r="J50" s="45" t="s">
-        <v>443</v>
-      </c>
-      <c r="K50" s="46" t="s">
-        <v>220</v>
+      <c r="F50" s="44" t="s">
+        <v>422</v>
+      </c>
+      <c r="G50" s="44" t="s">
+        <v>423</v>
+      </c>
+      <c r="H50" s="44" t="s">
+        <v>424</v>
+      </c>
+      <c r="I50" s="44" t="s">
+        <v>425</v>
+      </c>
+      <c r="J50" s="44" t="s">
+        <v>426</v>
+      </c>
+      <c r="K50" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="L50" s="6"/>
     </row>
     <row r="51" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A51" s="6"/>
       <c r="B51" s="33" t="s">
-        <v>444</v>
-      </c>
-      <c r="C51" s="42" t="s">
-        <v>445</v>
+        <v>427</v>
+      </c>
+      <c r="C51" s="41" t="s">
+        <v>428</v>
       </c>
       <c r="D51" s="34" t="s">
-        <v>446</v>
-      </c>
-      <c r="E51" s="45" t="s">
+        <v>429</v>
+      </c>
+      <c r="E51" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F51" s="45" t="s">
-        <v>296</v>
-      </c>
-      <c r="G51" s="45" t="s">
-        <v>210</v>
-      </c>
-      <c r="H51" s="45" t="s">
-        <v>447</v>
-      </c>
-      <c r="I51" s="45" t="s">
-        <v>448</v>
-      </c>
-      <c r="J51" s="45" t="s">
-        <v>449</v>
-      </c>
-      <c r="K51" s="46" t="s">
-        <v>450</v>
+      <c r="F51" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="G51" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="H51" s="44" t="s">
+        <v>430</v>
+      </c>
+      <c r="I51" s="44" t="s">
+        <v>431</v>
+      </c>
+      <c r="J51" s="44" t="s">
+        <v>432</v>
+      </c>
+      <c r="K51" s="45" t="s">
+        <v>433</v>
       </c>
       <c r="L51" s="6"/>
     </row>
     <row r="52" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A52" s="6"/>
       <c r="B52" s="33" t="s">
-        <v>451</v>
-      </c>
-      <c r="C52" s="42" t="s">
-        <v>452</v>
+        <v>434</v>
+      </c>
+      <c r="C52" s="41" t="s">
+        <v>435</v>
       </c>
       <c r="D52" s="34" t="s">
-        <v>453</v>
-      </c>
-      <c r="E52" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F52" s="45" t="s">
-        <v>322</v>
-      </c>
-      <c r="G52" s="45" t="s">
-        <v>210</v>
-      </c>
-      <c r="H52" s="45" t="s">
-        <v>454</v>
-      </c>
-      <c r="I52" s="45" t="s">
-        <v>448</v>
-      </c>
-      <c r="J52" s="45" t="s">
-        <v>455</v>
-      </c>
-      <c r="K52" s="46" t="s">
-        <v>456</v>
+        <v>436</v>
+      </c>
+      <c r="E52" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F52" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="G52" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="H52" s="44" t="s">
+        <v>437</v>
+      </c>
+      <c r="I52" s="44" t="s">
+        <v>431</v>
+      </c>
+      <c r="J52" s="44" t="s">
+        <v>438</v>
+      </c>
+      <c r="K52" s="45" t="s">
+        <v>439</v>
       </c>
       <c r="L52" s="6"/>
     </row>
     <row r="53" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A53" s="6"/>
       <c r="B53" s="33" t="s">
-        <v>457</v>
-      </c>
-      <c r="C53" s="42" t="s">
-        <v>458</v>
+        <v>440</v>
+      </c>
+      <c r="C53" s="41" t="s">
+        <v>441</v>
       </c>
       <c r="D53" s="34" t="s">
-        <v>459</v>
-      </c>
-      <c r="E53" s="45" t="s">
+        <v>442</v>
+      </c>
+      <c r="E53" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F53" s="45" t="s">
-        <v>460</v>
-      </c>
-      <c r="G53" s="45" t="s">
-        <v>280</v>
-      </c>
-      <c r="H53" s="45" t="s">
-        <v>461</v>
-      </c>
-      <c r="I53" s="45" t="s">
-        <v>462</v>
-      </c>
-      <c r="J53" s="45" t="s">
-        <v>463</v>
-      </c>
-      <c r="K53" s="46" t="s">
-        <v>464</v>
+      <c r="F53" s="44" t="s">
+        <v>443</v>
+      </c>
+      <c r="G53" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="H53" s="44" t="s">
+        <v>444</v>
+      </c>
+      <c r="I53" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="J53" s="44" t="s">
+        <v>446</v>
+      </c>
+      <c r="K53" s="45" t="s">
+        <v>447</v>
       </c>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="101.25" x14ac:dyDescent="0.2">
       <c r="A54" s="6"/>
       <c r="B54" s="33" t="s">
-        <v>465</v>
-      </c>
-      <c r="C54" s="42" t="s">
-        <v>466</v>
+        <v>486</v>
+      </c>
+      <c r="C54" s="41" t="s">
+        <v>487</v>
       </c>
       <c r="D54" s="34" t="s">
-        <v>467</v>
-      </c>
-      <c r="E54" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="E54" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F54" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="G54" s="45" t="s">
-        <v>469</v>
-      </c>
-      <c r="H54" s="45" t="s">
-        <v>470</v>
-      </c>
-      <c r="I54" s="45" t="s">
-        <v>448</v>
-      </c>
-      <c r="J54" s="45" t="s">
-        <v>471</v>
-      </c>
-      <c r="K54" s="46" t="s">
-        <v>220</v>
+      <c r="F54" s="44" t="s">
+        <v>357</v>
+      </c>
+      <c r="G54" s="44" t="s">
+        <v>489</v>
+      </c>
+      <c r="H54" s="44" t="s">
+        <v>488</v>
+      </c>
+      <c r="I54" s="44" t="s">
+        <v>490</v>
+      </c>
+      <c r="J54" s="44" t="s">
+        <v>449</v>
+      </c>
+      <c r="K54" s="45" t="s">
+        <v>491</v>
       </c>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" ht="45" x14ac:dyDescent="0.2">
       <c r="A55" s="6"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="42"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="45"/>
-      <c r="F55" s="45"/>
-      <c r="G55" s="45"/>
-      <c r="H55" s="45"/>
-      <c r="I55" s="45"/>
-      <c r="J55" s="45"/>
-      <c r="K55" s="46"/>
+      <c r="B55" s="33" t="s">
+        <v>476</v>
+      </c>
+      <c r="C55" s="41" t="s">
+        <v>477</v>
+      </c>
+      <c r="D55" s="34" t="s">
+        <v>475</v>
+      </c>
+      <c r="E55" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F55" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="G55" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="H55" s="44" t="s">
+        <v>478</v>
+      </c>
+      <c r="I55" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="J55" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="K55" s="45" t="s">
+        <v>479</v>
+      </c>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A56" s="6"/>
-      <c r="B56" s="33"/>
-      <c r="C56" s="42"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="45"/>
-      <c r="F56" s="45"/>
-      <c r="G56" s="45"/>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45"/>
-      <c r="J56" s="45"/>
-      <c r="K56" s="46"/>
+      <c r="B56" s="33" t="s">
+        <v>492</v>
+      </c>
+      <c r="C56" s="41" t="s">
+        <v>493</v>
+      </c>
+      <c r="D56" s="34" t="s">
+        <v>494</v>
+      </c>
+      <c r="E56" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F56" s="44" t="s">
+        <v>481</v>
+      </c>
+      <c r="G56" s="44" t="s">
+        <v>472</v>
+      </c>
+      <c r="H56" s="44" t="s">
+        <v>498</v>
+      </c>
+      <c r="I56" s="44" t="s">
+        <v>499</v>
+      </c>
+      <c r="J56" s="44"/>
+      <c r="K56" s="45"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
-      <c r="B57" s="33"/>
-      <c r="C57" s="42"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="45"/>
-      <c r="F57" s="45"/>
-      <c r="G57" s="45"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="45"/>
-      <c r="J57" s="45"/>
-      <c r="K57" s="46"/>
+      <c r="B57" s="33" t="s">
+        <v>500</v>
+      </c>
+      <c r="C57" s="41" t="s">
+        <v>501</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>495</v>
+      </c>
+      <c r="E57" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F57" s="44" t="s">
+        <v>481</v>
+      </c>
+      <c r="G57" s="44" t="s">
+        <v>472</v>
+      </c>
+      <c r="H57" s="44" t="s">
+        <v>498</v>
+      </c>
+      <c r="I57" s="44" t="s">
+        <v>499</v>
+      </c>
+      <c r="J57" s="44"/>
+      <c r="K57" s="45"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A58" s="6"/>
-      <c r="B58" s="33"/>
-      <c r="C58" s="42"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="45"/>
-      <c r="F58" s="45"/>
-      <c r="G58" s="45"/>
-      <c r="H58" s="45"/>
-      <c r="I58" s="45"/>
-      <c r="J58" s="45"/>
-      <c r="K58" s="46"/>
+      <c r="B58" s="33" t="s">
+        <v>502</v>
+      </c>
+      <c r="C58" s="41" t="s">
+        <v>503</v>
+      </c>
+      <c r="D58" s="34" t="s">
+        <v>496</v>
+      </c>
+      <c r="E58" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="F58" s="44" t="s">
+        <v>481</v>
+      </c>
+      <c r="G58" s="44" t="s">
+        <v>504</v>
+      </c>
+      <c r="H58" s="44" t="s">
+        <v>505</v>
+      </c>
+      <c r="I58" s="44" t="s">
+        <v>499</v>
+      </c>
+      <c r="J58" s="44"/>
+      <c r="K58" s="45"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="68.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
-      <c r="B59" s="37"/>
-      <c r="C59" s="50"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="51"/>
-      <c r="G59" s="51"/>
-      <c r="H59" s="51"/>
-      <c r="I59" s="51"/>
-      <c r="J59" s="51"/>
-      <c r="K59" s="52"/>
+      <c r="B59" s="37" t="s">
+        <v>506</v>
+      </c>
+      <c r="C59" s="49" t="s">
+        <v>507</v>
+      </c>
+      <c r="D59" s="34" t="s">
+        <v>497</v>
+      </c>
+      <c r="E59" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="F59" s="44" t="s">
+        <v>357</v>
+      </c>
+      <c r="G59" s="50" t="s">
+        <v>508</v>
+      </c>
+      <c r="H59" s="50" t="s">
+        <v>509</v>
+      </c>
+      <c r="I59" s="50" t="s">
+        <v>510</v>
+      </c>
+      <c r="J59" s="50"/>
+      <c r="K59" s="51"/>
       <c r="L59" s="6"/>
     </row>
     <row r="60" spans="1:12" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
@@ -8036,7 +8224,7 @@
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
-      <c r="G60" s="69"/>
+      <c r="G60" s="68"/>
       <c r="H60" s="6"/>
       <c r="I60" s="6"/>
       <c r="J60" s="6"/>
@@ -8050,7 +8238,7 @@
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
-      <c r="G61" s="69"/>
+      <c r="G61" s="68"/>
       <c r="H61" s="6"/>
       <c r="I61" s="6"/>
       <c r="J61" s="6"/>
@@ -8064,7 +8252,7 @@
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
-      <c r="G62" s="69"/>
+      <c r="G62" s="68"/>
       <c r="H62" s="6"/>
       <c r="I62" s="6"/>
       <c r="J62" s="6"/>
@@ -8078,7 +8266,7 @@
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
-      <c r="G63" s="69"/>
+      <c r="G63" s="68"/>
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
@@ -8092,7 +8280,7 @@
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
-      <c r="G64" s="69"/>
+      <c r="G64" s="68"/>
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
@@ -8106,7 +8294,7 @@
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
-      <c r="G65" s="69"/>
+      <c r="G65" s="68"/>
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
       <c r="J65" s="6"/>
@@ -8120,7 +8308,7 @@
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
-      <c r="G66" s="69"/>
+      <c r="G66" s="68"/>
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
@@ -8134,7 +8322,7 @@
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
-      <c r="G67" s="69"/>
+      <c r="G67" s="68"/>
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
@@ -8148,7 +8336,7 @@
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
-      <c r="G68" s="69"/>
+      <c r="G68" s="68"/>
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
@@ -8162,7 +8350,7 @@
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
-      <c r="G69" s="69"/>
+      <c r="G69" s="68"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
@@ -8176,7 +8364,7 @@
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
-      <c r="G70" s="69"/>
+      <c r="G70" s="68"/>
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
@@ -8190,7 +8378,7 @@
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
-      <c r="G71" s="69"/>
+      <c r="G71" s="68"/>
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
       <c r="J71" s="6"/>
@@ -8204,7 +8392,7 @@
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
-      <c r="G72" s="69"/>
+      <c r="G72" s="68"/>
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
       <c r="J72" s="6"/>
@@ -8218,7 +8406,7 @@
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
-      <c r="G73" s="69"/>
+      <c r="G73" s="68"/>
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
       <c r="J73" s="6"/>
@@ -8232,7 +8420,7 @@
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
-      <c r="G74" s="69"/>
+      <c r="G74" s="68"/>
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
       <c r="J74" s="6"/>
@@ -8246,7 +8434,7 @@
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
-      <c r="G75" s="69"/>
+      <c r="G75" s="68"/>
       <c r="H75" s="6"/>
       <c r="I75" s="6"/>
       <c r="J75" s="6"/>
@@ -8260,7 +8448,7 @@
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
-      <c r="G76" s="69"/>
+      <c r="G76" s="68"/>
       <c r="H76" s="6"/>
       <c r="I76" s="6"/>
       <c r="J76" s="6"/>
@@ -8274,7 +8462,7 @@
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
-      <c r="G77" s="69"/>
+      <c r="G77" s="68"/>
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
       <c r="J77" s="6"/>
@@ -8288,7 +8476,7 @@
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
-      <c r="G78" s="69"/>
+      <c r="G78" s="68"/>
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
@@ -8302,7 +8490,7 @@
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
-      <c r="G79" s="69"/>
+      <c r="G79" s="68"/>
       <c r="H79" s="6"/>
       <c r="I79" s="6"/>
       <c r="J79" s="6"/>
@@ -8316,7 +8504,7 @@
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
-      <c r="G80" s="69"/>
+      <c r="G80" s="68"/>
       <c r="H80" s="6"/>
       <c r="I80" s="6"/>
       <c r="J80" s="6"/>
@@ -8330,7 +8518,7 @@
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
-      <c r="G81" s="69"/>
+      <c r="G81" s="68"/>
       <c r="H81" s="6"/>
       <c r="I81" s="6"/>
       <c r="J81" s="6"/>
@@ -8344,7 +8532,7 @@
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
-      <c r="G82" s="69"/>
+      <c r="G82" s="68"/>
       <c r="H82" s="6"/>
       <c r="I82" s="6"/>
       <c r="J82" s="6"/>
@@ -8358,7 +8546,7 @@
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
-      <c r="G83" s="69"/>
+      <c r="G83" s="68"/>
       <c r="H83" s="6"/>
       <c r="I83" s="6"/>
       <c r="J83" s="6"/>
@@ -11025,6 +11213,7 @@
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B4:K4"/>
   </mergeCells>
+  <phoneticPr fontId="28" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D59" xr:uid="{9519DAB4-5B27-47AE-BDE4-092489328B4E}">
       <formula1>Estimation</formula1>
@@ -11037,7 +11226,11 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="27ec883c-a62c-444f-a935-fcddb579e39d" ContentTypeId="0x0101008B4DD370EC31429186F3AD49F0D3098F00D44DBCB9EB4F45278CB5C9765BE52995" PreviousValue="false"/>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>OECDListFormCollapsible</Display>
+  <Edit>OECDListFormCollapsible</Edit>
+  <New>OECDListFormCollapsible</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11245,18 +11438,19 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>OECDListFormCollapsible</Display>
-  <Edit>OECDListFormCollapsible</Edit>
-  <New>OECDListFormCollapsible</New>
-</FormTemplates>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="27ec883c-a62c-444f-a935-fcddb579e39d" ContentTypeId="0x0101008B4DD370EC31429186F3AD49F0D3098F00D44DBCB9EB4F45278CB5C9765BE52995" PreviousValue="false"/>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties">
-  <LongProp xmlns="" name="OECDProjectMembers"><![CDATA[125;#DEDEYN Duniya, SKC/VET;#186;#GMEINDER Michael, ELS/HD;#93;#MORGAN David, ELS/HD;#51;#VALLARD Isabelle, ELS/HD;#213;#CANAUD Marie-Clémence, ELS/HD;#582;#ROCARD Eileen, ELS/HD;#476;#WILKENS Jens, ELS/HD;#322;#BALESTAT Gaëlle, ELS/HD;#126;#JAMES Chris, ELS/HD;#630;#LECH Lukasz, CFE/COM;#182;#MUELLER Michael, ELS/HD;#1521;#COOPER James, ELS/HD;#1606;#LUSTIG Sebastiano, ELS/HD;#1604;#FINOT Abigail, ELS/HD;#2402;#GUANAIS Frederico, ELS/HD;#4354;#DEZIEL Justine, GOV/MAPS;#5000;#SOYKAN Sahnur, ELS/HD;#5393;#MILSTEIN Ricarda, ELS/HD;#219;#FRON Pauline, ELS/SPD;#6472;#PUTLAND Mark, ELS/HD]]></LongProp>
-  <LongProp xmlns="" name="TaxCatchAll"><![CDATA[1035;#Health Data|fea3c97f-c347-4c31-aa9e-846c416ae64d;#1034;#Health Accounts|a7d573e0-71ab-4a13-bf19-135df7106c85;#28;#Health Committee|2c0321da-353b-4c28-8e89-93836ce9b975;#44;#ELS/HD|b8c03ca5-edf2-4d31-8dc8-b63884972abf;#210;#Health|65dc2cd1-a1c3-4b24-a1e5-75b3cdf95ba5;#867;#2017-18|ffda23c2-cd1b-45cc-b3f4-67b12010cc58]]></LongProp>
-</LongProperties>
+<?mso-contentType ?>
+<CtFieldPriority xmlns="http://www.oecd.org/eshare/projectsentre/CtFieldPriority/" xmlns:i="http://www.w3.org/2001/XMLSchema-instance">
+  <PriorityFields xmlns:a="http://schemas.microsoft.com/2003/10/Serialization/Arrays">
+    <a:string>Title</a:string>
+    <a:string>OECDCountry</a:string>
+    <a:string>OECDTopic</a:string>
+    <a:string>OECDKeywords</a:string>
+  </PriorityFields>
+</CtFieldPriority>
 </file>
 
 <file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11691,21 +11885,16 @@
 </file>
 
 <file path=customXml/item6.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<CtFieldPriority xmlns="http://www.oecd.org/eshare/projectsentre/CtFieldPriority/" xmlns:i="http://www.w3.org/2001/XMLSchema-instance">
-  <PriorityFields xmlns:a="http://schemas.microsoft.com/2003/10/Serialization/Arrays">
-    <a:string>Title</a:string>
-    <a:string>OECDCountry</a:string>
-    <a:string>OECDTopic</a:string>
-    <a:string>OECDKeywords</a:string>
-  </PriorityFields>
-</CtFieldPriority>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties">
+  <LongProp xmlns="" name="OECDProjectMembers"><![CDATA[125;#DEDEYN Duniya, SKC/VET;#186;#GMEINDER Michael, ELS/HD;#93;#MORGAN David, ELS/HD;#51;#VALLARD Isabelle, ELS/HD;#213;#CANAUD Marie-Clémence, ELS/HD;#582;#ROCARD Eileen, ELS/HD;#476;#WILKENS Jens, ELS/HD;#322;#BALESTAT Gaëlle, ELS/HD;#126;#JAMES Chris, ELS/HD;#630;#LECH Lukasz, CFE/COM;#182;#MUELLER Michael, ELS/HD;#1521;#COOPER James, ELS/HD;#1606;#LUSTIG Sebastiano, ELS/HD;#1604;#FINOT Abigail, ELS/HD;#2402;#GUANAIS Frederico, ELS/HD;#4354;#DEZIEL Justine, GOV/MAPS;#5000;#SOYKAN Sahnur, ELS/HD;#5393;#MILSTEIN Ricarda, ELS/HD;#219;#FRON Pauline, ELS/SPD;#6472;#PUTLAND Mark, ELS/HD]]></LongProp>
+  <LongProp xmlns="" name="TaxCatchAll"><![CDATA[1035;#Health Data|fea3c97f-c347-4c31-aa9e-846c416ae64d;#1034;#Health Accounts|a7d573e0-71ab-4a13-bf19-135df7106c85;#28;#Health Committee|2c0321da-353b-4c28-8e89-93836ce9b975;#44;#ELS/HD|b8c03ca5-edf2-4d31-8dc8-b63884972abf;#210;#Health|65dc2cd1-a1c3-4b24-a1e5-75b3cdf95ba5;#867;#2017-18|ffda23c2-cd1b-45cc-b3f4-67b12010cc58]]></LongProp>
+</LongProperties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4799DB5-0CFD-43B5-BDAB-C574BE734A75}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D78348B7-97C1-4BD6-9014-6EC11F47DCD2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11726,18 +11915,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D78348B7-97C1-4BD6-9014-6EC11F47DCD2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4799DB5-0CFD-43B5-BDAB-C574BE734A75}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB1F8357-599A-44D1-AACE-AD9098E6247B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FCD22A6-7F4A-4477-B9B2-16E048FDC0D9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
-    <ds:schemaRef ds:uri=""/>
+    <ds:schemaRef ds:uri="http://www.oecd.org/eshare/projectsentre/CtFieldPriority/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/2003/10/Serialization/Arrays"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11766,10 +11955,10 @@
 </file>
 
 <file path=customXml/itemProps6.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FCD22A6-7F4A-4477-B9B2-16E048FDC0D9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB1F8357-599A-44D1-AACE-AD9098E6247B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.oecd.org/eshare/projectsentre/CtFieldPriority/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/2003/10/Serialization/Arrays"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+    <ds:schemaRef ds:uri=""/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>